--- a/DemandForecast/MT_Demand_Forecast_SOP_Model.xlsx
+++ b/DemandForecast/MT_Demand_Forecast_SOP_Model.xlsx
@@ -262,6 +262,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00808080"/>
       <sz val="8.5"/>
     </font>
@@ -284,12 +290,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="002E5496"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -386,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -492,45 +492,45 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="39" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="39" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="39" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="39" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="40" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="37" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="38" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="42" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -552,11 +552,17 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="15" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="37" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="38" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3266,7 +3272,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B4:B19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NPI Launch,Product Relaunch,New Listing,Distribution Expansion,Store Expansion,Visibility Campaign,Endcap,Power Wing,Gondola,SIS,Counter Display,Festival Promotion,BOGO,Price Drop,Retail Festival,Digital Campaign,TV Campaign,Influencer Campaign,Consumer Offer,Sampling Activity,Bundle Promotion,Combo Pack,Seasonal Push,New Warehouse Opening,New Distributor,Market Expansion,Export Order,Institutional Sales,Clearance Campaign"</formula1>
+      <formula1>'Event Settings'!$G$3:$G$31</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3577,7 +3583,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B4:B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NPI Launch,Product Relaunch,New Listing,Distribution Expansion,Store Expansion,Visibility Campaign,Endcap,Power Wing,Gondola,SIS,Counter Display,Festival Promotion,BOGO,Price Drop,Retail Festival,Digital Campaign,TV Campaign,Influencer Campaign,Consumer Offer,Sampling Activity,Bundle Promotion,Combo Pack,Seasonal Push,New Warehouse Opening,New Distributor,Market Expansion,Export Order,Institutional Sales,Clearance Campaign"</formula1>
+      <formula1>'Event Settings'!$G$3:$G$31</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3884,12 +3890,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3905,6 +3912,11 @@
           <t>All event uplift assumptions are maintained centrally here. Blue cells are editable.</t>
         </is>
       </c>
+      <c r="G2" s="88" t="inlineStr">
+        <is>
+          <t>Event Type list</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -3912,6 +3924,11 @@
           <t>1 · Conversion &amp; margin</t>
         </is>
       </c>
+      <c r="G3" s="89" t="inlineStr">
+        <is>
+          <t>NPI Launch</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
@@ -3927,6 +3944,11 @@
           <t>real portfolio avg primary NSV ÷ units; used for unit↔value conversion</t>
         </is>
       </c>
+      <c r="G4" s="89" t="inlineStr">
+        <is>
+          <t>Product Relaunch</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
@@ -3937,6 +3959,11 @@
       <c r="B5" s="24" t="n">
         <v>0.52</v>
       </c>
+      <c r="G5" s="89" t="inlineStr">
+        <is>
+          <t>New Listing</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
@@ -3947,6 +3974,11 @@
       <c r="B6" s="27" t="n">
         <v>1</v>
       </c>
+      <c r="G6" s="89" t="inlineStr">
+        <is>
+          <t>Distribution Expansion</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -3964,6 +3996,18 @@
           <t>overlapping % events combine multiplicatively: 1−Π(1+uᵢ) not simple sum</t>
         </is>
       </c>
+      <c r="G7" s="89" t="inlineStr">
+        <is>
+          <t>Store Expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" s="89" t="inlineStr">
+        <is>
+          <t>Visibility Campaign</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -3971,6 +4015,11 @@
           <t>2 · Event Priority weights</t>
         </is>
       </c>
+      <c r="G9" s="89" t="inlineStr">
+        <is>
+          <t>Endcap</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -3983,6 +4032,11 @@
           <t>Weight</t>
         </is>
       </c>
+      <c r="G10" s="89" t="inlineStr">
+        <is>
+          <t>Power Wing</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -3990,8 +4044,13 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="B11" s="88" t="n">
+      <c r="B11" s="90" t="n">
         <v>1</v>
+      </c>
+      <c r="G11" s="89" t="inlineStr">
+        <is>
+          <t>Gondola</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4000,8 +4059,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="B12" s="88" t="n">
+      <c r="B12" s="90" t="n">
         <v>0.85</v>
+      </c>
+      <c r="G12" s="89" t="inlineStr">
+        <is>
+          <t>SIS</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4010,8 +4074,13 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="B13" s="88" t="n">
+      <c r="B13" s="90" t="n">
         <v>0.6</v>
+      </c>
+      <c r="G13" s="89" t="inlineStr">
+        <is>
+          <t>Counter Display</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4020,8 +4089,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="B14" s="88" t="n">
+      <c r="B14" s="90" t="n">
         <v>0.35</v>
+      </c>
+      <c r="G14" s="89" t="inlineStr">
+        <is>
+          <t>Festival Promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" s="89" t="inlineStr">
+        <is>
+          <t>BOGO</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -4030,6 +4111,11 @@
           <t>3 · NPI / structural Ramp-up curve (share of full effect by month-in-life)</t>
         </is>
       </c>
+      <c r="G16" s="89" t="inlineStr">
+        <is>
+          <t>Price Drop</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -4042,53 +4128,95 @@
           <t>Ramp %</t>
         </is>
       </c>
+      <c r="G17" s="89" t="inlineStr">
+        <is>
+          <t>Retail Festival</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="89" t="n">
+      <c r="A18" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="90" t="n">
+      <c r="B18" s="92" t="n">
         <v>0.3</v>
       </c>
+      <c r="G18" s="89" t="inlineStr">
+        <is>
+          <t>Digital Campaign</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="89" t="n">
+      <c r="A19" s="91" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="90" t="n">
+      <c r="B19" s="92" t="n">
         <v>0.6</v>
       </c>
+      <c r="G19" s="89" t="inlineStr">
+        <is>
+          <t>TV Campaign</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="89" t="n">
+      <c r="A20" s="91" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="90" t="n">
+      <c r="B20" s="92" t="n">
         <v>0.85</v>
       </c>
+      <c r="G20" s="89" t="inlineStr">
+        <is>
+          <t>Influencer Campaign</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="89" t="n">
+      <c r="A21" s="91" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="90" t="n">
+      <c r="B21" s="92" t="n">
         <v>1</v>
       </c>
+      <c r="G21" s="89" t="inlineStr">
+        <is>
+          <t>Consumer Offer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="89" t="n">
+      <c r="A22" s="91" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="90" t="n">
+      <c r="B22" s="92" t="n">
         <v>1</v>
       </c>
+      <c r="G22" s="89" t="inlineStr">
+        <is>
+          <t>Sampling Activity</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="89" t="n">
+      <c r="A23" s="91" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="90" t="n">
+      <c r="B23" s="92" t="n">
         <v>1</v>
+      </c>
+      <c r="G23" s="89" t="inlineStr">
+        <is>
+          <t>Bundle Promotion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" s="89" t="inlineStr">
+        <is>
+          <t>Combo Pack</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -4097,6 +4225,11 @@
           <t>4 · Promotion effect decay (share of peak after the promo month)</t>
         </is>
       </c>
+      <c r="G25" s="89" t="inlineStr">
+        <is>
+          <t>Seasonal Push</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -4109,37 +4242,69 @@
           <t>Decay %</t>
         </is>
       </c>
+      <c r="G26" s="89" t="inlineStr">
+        <is>
+          <t>New Warehouse Opening</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="B27" s="90" t="n">
+      <c r="A27" s="91" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" s="92" t="n">
         <v>1</v>
       </c>
+      <c r="G27" s="89" t="inlineStr">
+        <is>
+          <t>New Distributor</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="89" t="n">
+      <c r="A28" s="91" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="90" t="n">
+      <c r="B28" s="92" t="n">
         <v>0.5</v>
       </c>
+      <c r="G28" s="89" t="inlineStr">
+        <is>
+          <t>Market Expansion</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="89" t="n">
+      <c r="A29" s="91" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="90" t="n">
+      <c r="B29" s="92" t="n">
         <v>0.25</v>
       </c>
+      <c r="G29" s="89" t="inlineStr">
+        <is>
+          <t>Export Order</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="89" t="n">
+      <c r="A30" s="91" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="90" t="n">
-        <v>0</v>
+      <c r="B30" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="89" t="inlineStr">
+        <is>
+          <t>Institutional Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="G31" s="89" t="inlineStr">
+        <is>
+          <t>Clearance Campaign</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -4162,7 +4327,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="89" t="inlineStr">
+      <c r="A34" s="91" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -4174,7 +4339,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="89" t="inlineStr">
+      <c r="A35" s="91" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -4186,7 +4351,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="89" t="inlineStr">
+      <c r="A36" s="91" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
@@ -4198,7 +4363,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="89" t="inlineStr">
+      <c r="A37" s="91" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
@@ -4267,7 +4432,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="91">
+      <c r="A4" s="93">
         <f>SUMIFS('Monthly Target Upload'!$D$4:$D$15,'Monthly Target Upload'!$A$4:$A$15,'Control Panel'!$B$4)+SUMIFS('Monthly Target Upload'!$D$4:$D$15,'Monthly Target Upload'!$A$4:$A$15,'Control Panel'!$B$6)+SUMIFS('Monthly Target Upload'!$D$4:$D$15,'Monthly Target Upload'!$A$4:$A$15,'Control Panel'!$B$7)</f>
         <v/>
       </c>
@@ -4432,7 +4597,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="92" t="inlineStr">
+      <c r="A13" s="94" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -4449,7 +4614,7 @@
         <f>SUM(D8:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="92" t="n"/>
+      <c r="E13" s="94" t="n"/>
       <c r="F13" s="18">
         <f>SUM(F8:F12)</f>
         <v/>
@@ -4461,7 +4626,7 @@
           <t>Reconciliation vs company target</t>
         </is>
       </c>
-      <c r="E14" s="93" t="inlineStr">
+      <c r="E14" s="95" t="inlineStr">
         <is>
           <t>OK if 0 →</t>
         </is>
@@ -5431,7 +5596,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="92" t="inlineStr">
+      <c r="A58" s="94" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -5448,7 +5613,7 @@
         <f>SUM(D18:D57)</f>
         <v/>
       </c>
-      <c r="E58" s="92" t="n"/>
+      <c r="E58" s="94" t="n"/>
       <c r="F58" s="18">
         <f>SUM(F18:F57)</f>
         <v/>
@@ -5460,7 +5625,7 @@
           <t>Reconciliation vs company target</t>
         </is>
       </c>
-      <c r="E59" s="93" t="inlineStr">
+      <c r="E59" s="95" t="inlineStr">
         <is>
           <t>OK if 0 →</t>
         </is>
@@ -6085,7 +6250,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="92" t="inlineStr">
+      <c r="A88" s="94" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -6102,7 +6267,7 @@
         <f>SUM(D63:D87)</f>
         <v/>
       </c>
-      <c r="E88" s="92" t="n"/>
+      <c r="E88" s="94" t="n"/>
       <c r="F88" s="18">
         <f>SUM(F63:F87)</f>
         <v/>
@@ -6114,7 +6279,7 @@
           <t>Reconciliation vs company target</t>
         </is>
       </c>
-      <c r="E89" s="93" t="inlineStr">
+      <c r="E89" s="95" t="inlineStr">
         <is>
           <t>OK if 0 →</t>
         </is>
@@ -7084,7 +7249,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="92" t="inlineStr">
+      <c r="A133" s="94" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -7101,7 +7266,7 @@
         <f>SUM(D93:D132)</f>
         <v/>
       </c>
-      <c r="E133" s="92" t="n"/>
+      <c r="E133" s="94" t="n"/>
       <c r="F133" s="18">
         <f>SUM(F93:F132)</f>
         <v/>
@@ -7113,7 +7278,7 @@
           <t>Reconciliation vs company target</t>
         </is>
       </c>
-      <c r="E134" s="93" t="inlineStr">
+      <c r="E134" s="95" t="inlineStr">
         <is>
           <t>OK if 0 →</t>
         </is>
@@ -7709,7 +7874,7 @@
         <f>'Distributor Master'!$A$4</f>
         <v/>
       </c>
-      <c r="B4" s="94">
+      <c r="B4" s="96">
         <f>'Distributor Master'!$C$4</f>
         <v/>
       </c>
@@ -7747,7 +7912,7 @@
         <f>'Distributor Master'!$A$5</f>
         <v/>
       </c>
-      <c r="B5" s="94">
+      <c r="B5" s="96">
         <f>'Distributor Master'!$C$5</f>
         <v/>
       </c>
@@ -7785,7 +7950,7 @@
         <f>'Distributor Master'!$A$6</f>
         <v/>
       </c>
-      <c r="B6" s="94">
+      <c r="B6" s="96">
         <f>'Distributor Master'!$C$6</f>
         <v/>
       </c>
@@ -7823,7 +7988,7 @@
         <f>'Distributor Master'!$A$7</f>
         <v/>
       </c>
-      <c r="B7" s="94">
+      <c r="B7" s="96">
         <f>'Distributor Master'!$C$7</f>
         <v/>
       </c>
@@ -7861,7 +8026,7 @@
         <f>'Distributor Master'!$A$8</f>
         <v/>
       </c>
-      <c r="B8" s="94">
+      <c r="B8" s="96">
         <f>'Distributor Master'!$C$8</f>
         <v/>
       </c>
@@ -7899,7 +8064,7 @@
         <f>'Distributor Master'!$A$9</f>
         <v/>
       </c>
-      <c r="B9" s="94">
+      <c r="B9" s="96">
         <f>'Distributor Master'!$C$9</f>
         <v/>
       </c>
@@ -7937,7 +8102,7 @@
         <f>'Distributor Master'!$A$10</f>
         <v/>
       </c>
-      <c r="B10" s="94">
+      <c r="B10" s="96">
         <f>'Distributor Master'!$C$10</f>
         <v/>
       </c>
@@ -7975,7 +8140,7 @@
         <f>'Distributor Master'!$A$11</f>
         <v/>
       </c>
-      <c r="B11" s="94">
+      <c r="B11" s="96">
         <f>'Distributor Master'!$C$11</f>
         <v/>
       </c>
@@ -8013,7 +8178,7 @@
         <f>'Distributor Master'!$A$12</f>
         <v/>
       </c>
-      <c r="B12" s="94">
+      <c r="B12" s="96">
         <f>'Distributor Master'!$C$12</f>
         <v/>
       </c>
@@ -8051,7 +8216,7 @@
         <f>'Distributor Master'!$A$13</f>
         <v/>
       </c>
-      <c r="B13" s="94">
+      <c r="B13" s="96">
         <f>'Distributor Master'!$C$13</f>
         <v/>
       </c>
@@ -8089,7 +8254,7 @@
         <f>'Distributor Master'!$A$14</f>
         <v/>
       </c>
-      <c r="B14" s="94">
+      <c r="B14" s="96">
         <f>'Distributor Master'!$C$14</f>
         <v/>
       </c>
@@ -8127,7 +8292,7 @@
         <f>'Distributor Master'!$A$15</f>
         <v/>
       </c>
-      <c r="B15" s="94">
+      <c r="B15" s="96">
         <f>'Distributor Master'!$C$15</f>
         <v/>
       </c>
@@ -8165,7 +8330,7 @@
         <f>'Distributor Master'!$A$16</f>
         <v/>
       </c>
-      <c r="B16" s="94">
+      <c r="B16" s="96">
         <f>'Distributor Master'!$C$16</f>
         <v/>
       </c>
@@ -8203,7 +8368,7 @@
         <f>'Distributor Master'!$A$17</f>
         <v/>
       </c>
-      <c r="B17" s="94">
+      <c r="B17" s="96">
         <f>'Distributor Master'!$C$17</f>
         <v/>
       </c>
@@ -8241,7 +8406,7 @@
         <f>'Distributor Master'!$A$18</f>
         <v/>
       </c>
-      <c r="B18" s="94">
+      <c r="B18" s="96">
         <f>'Distributor Master'!$C$18</f>
         <v/>
       </c>
@@ -8279,7 +8444,7 @@
         <f>'Distributor Master'!$A$19</f>
         <v/>
       </c>
-      <c r="B19" s="94">
+      <c r="B19" s="96">
         <f>'Distributor Master'!$C$19</f>
         <v/>
       </c>
@@ -8317,7 +8482,7 @@
         <f>'Distributor Master'!$A$20</f>
         <v/>
       </c>
-      <c r="B20" s="94">
+      <c r="B20" s="96">
         <f>'Distributor Master'!$C$20</f>
         <v/>
       </c>
@@ -8355,7 +8520,7 @@
         <f>'Distributor Master'!$A$21</f>
         <v/>
       </c>
-      <c r="B21" s="94">
+      <c r="B21" s="96">
         <f>'Distributor Master'!$C$21</f>
         <v/>
       </c>
@@ -8393,7 +8558,7 @@
         <f>'Distributor Master'!$A$22</f>
         <v/>
       </c>
-      <c r="B22" s="94">
+      <c r="B22" s="96">
         <f>'Distributor Master'!$C$22</f>
         <v/>
       </c>
@@ -8431,7 +8596,7 @@
         <f>'Distributor Master'!$A$23</f>
         <v/>
       </c>
-      <c r="B23" s="94">
+      <c r="B23" s="96">
         <f>'Distributor Master'!$C$23</f>
         <v/>
       </c>
@@ -8469,7 +8634,7 @@
         <f>'Distributor Master'!$A$24</f>
         <v/>
       </c>
-      <c r="B24" s="94">
+      <c r="B24" s="96">
         <f>'Distributor Master'!$C$24</f>
         <v/>
       </c>
@@ -8507,7 +8672,7 @@
         <f>'Distributor Master'!$A$25</f>
         <v/>
       </c>
-      <c r="B25" s="94">
+      <c r="B25" s="96">
         <f>'Distributor Master'!$C$25</f>
         <v/>
       </c>
@@ -8545,7 +8710,7 @@
         <f>'Distributor Master'!$A$26</f>
         <v/>
       </c>
-      <c r="B26" s="94">
+      <c r="B26" s="96">
         <f>'Distributor Master'!$C$26</f>
         <v/>
       </c>
@@ -8583,7 +8748,7 @@
         <f>'Distributor Master'!$A$27</f>
         <v/>
       </c>
-      <c r="B27" s="94">
+      <c r="B27" s="96">
         <f>'Distributor Master'!$C$27</f>
         <v/>
       </c>
@@ -8621,7 +8786,7 @@
         <f>'Distributor Master'!$A$28</f>
         <v/>
       </c>
-      <c r="B28" s="94">
+      <c r="B28" s="96">
         <f>'Distributor Master'!$C$28</f>
         <v/>
       </c>
@@ -8659,7 +8824,7 @@
         <f>'Distributor Master'!$A$29</f>
         <v/>
       </c>
-      <c r="B29" s="94">
+      <c r="B29" s="96">
         <f>'Distributor Master'!$C$29</f>
         <v/>
       </c>
@@ -8697,7 +8862,7 @@
         <f>'Distributor Master'!$A$30</f>
         <v/>
       </c>
-      <c r="B30" s="94">
+      <c r="B30" s="96">
         <f>'Distributor Master'!$C$30</f>
         <v/>
       </c>
@@ -8735,7 +8900,7 @@
         <f>'Distributor Master'!$A$31</f>
         <v/>
       </c>
-      <c r="B31" s="94">
+      <c r="B31" s="96">
         <f>'Distributor Master'!$C$31</f>
         <v/>
       </c>
@@ -8773,7 +8938,7 @@
         <f>'Distributor Master'!$A$32</f>
         <v/>
       </c>
-      <c r="B32" s="94">
+      <c r="B32" s="96">
         <f>'Distributor Master'!$C$32</f>
         <v/>
       </c>
@@ -8811,7 +8976,7 @@
         <f>'Distributor Master'!$A$33</f>
         <v/>
       </c>
-      <c r="B33" s="94">
+      <c r="B33" s="96">
         <f>'Distributor Master'!$C$33</f>
         <v/>
       </c>
@@ -9496,7 +9661,7 @@
       <c r="C5" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="D5" s="95">
+      <c r="D5" s="97">
         <f>'Control Panel'!$B$53</f>
         <v/>
       </c>
@@ -9535,7 +9700,7 @@
       <c r="C6" s="33" t="n">
         <v>0.28</v>
       </c>
-      <c r="D6" s="95">
+      <c r="D6" s="97">
         <f>'Control Panel'!$B$54</f>
         <v/>
       </c>
@@ -9574,7 +9739,7 @@
       <c r="C7" s="33" t="n">
         <v>0.27</v>
       </c>
-      <c r="D7" s="95">
+      <c r="D7" s="97">
         <f>'Control Panel'!$B$55</f>
         <v/>
       </c>
@@ -9613,7 +9778,7 @@
       <c r="C8" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="D8" s="95">
+      <c r="D8" s="97">
         <f>'Control Panel'!$B$56</f>
         <v/>
       </c>
@@ -9669,32 +9834,32 @@
       <c r="I9" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="96" t="inlineStr">
+      <c r="A11" s="98" t="inlineStr">
         <is>
           <t>Overload alerts:</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="97">
+      <c r="A12" s="99">
         <f>IF(I5&gt;1,A5&amp;" over capacity — reallocate "&amp;TEXT(MAX(E5:G5)-D5,"0.0")&amp;" Cr","")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="97">
+      <c r="A13" s="99">
         <f>IF(I6&gt;1,A6&amp;" over capacity — reallocate "&amp;TEXT(MAX(E6:G6)-D6,"0.0")&amp;" Cr","")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="97">
+      <c r="A14" s="99">
         <f>IF(I7&gt;1,A7&amp;" over capacity — reallocate "&amp;TEXT(MAX(E7:G7)-D7,"0.0")&amp;" Cr","")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="97">
+      <c r="A15" s="99">
         <f>IF(I8&gt;1,A8&amp;" over capacity — reallocate "&amp;TEXT(MAX(E8:G8)-D8,"0.0")&amp;" Cr","")</f>
         <v/>
       </c>
@@ -9789,7 +9954,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="89" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>Jul'25</t>
         </is>
@@ -9824,7 +9989,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="89" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>Aug'25</t>
         </is>
@@ -9859,7 +10024,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="89" t="inlineStr">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>Sep'25</t>
         </is>
@@ -9894,7 +10059,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="89" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>Oct'25</t>
         </is>
@@ -9929,7 +10094,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="89" t="inlineStr">
+      <c r="A8" s="91" t="inlineStr">
         <is>
           <t>Nov'25</t>
         </is>
@@ -9964,7 +10129,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="89" t="inlineStr">
+      <c r="A9" s="91" t="inlineStr">
         <is>
           <t>Dec'25</t>
         </is>
@@ -9999,7 +10164,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="89" t="inlineStr">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>Jan'25</t>
         </is>
@@ -10034,7 +10199,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="89" t="inlineStr">
+      <c r="A11" s="91" t="inlineStr">
         <is>
           <t>Feb'25</t>
         </is>
@@ -10069,7 +10234,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="89" t="inlineStr">
+      <c r="A12" s="91" t="inlineStr">
         <is>
           <t>Mar'25</t>
         </is>
@@ -10104,7 +10269,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="89" t="inlineStr">
+      <c r="A13" s="91" t="inlineStr">
         <is>
           <t>Apr'26</t>
         </is>
@@ -10139,7 +10304,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="89" t="inlineStr">
+      <c r="A14" s="91" t="inlineStr">
         <is>
           <t>May'26</t>
         </is>
@@ -10186,7 +10351,7 @@
           <t>MAPE</t>
         </is>
       </c>
-      <c r="B17" s="98">
+      <c r="B17" s="100">
         <f>AVERAGE(F4:F14)</f>
         <v/>
       </c>
@@ -10197,7 +10362,7 @@
           <t>WMAPE</t>
         </is>
       </c>
-      <c r="B18" s="98">
+      <c r="B18" s="100">
         <f>SUM(E4:E14)/SUM(C4:C14)</f>
         <v/>
       </c>
@@ -10208,7 +10373,7 @@
           <t>Forecast Bias (Σerr/Σactual)</t>
         </is>
       </c>
-      <c r="B19" s="98">
+      <c r="B19" s="100">
         <f>SUM(D4:D14)/SUM(C4:C14)</f>
         <v/>
       </c>
@@ -10219,7 +10384,7 @@
           <t>Tracking Signal (Σerr/MAD)</t>
         </is>
       </c>
-      <c r="B20" s="99">
+      <c r="B20" s="101">
         <f>IFERROR(SUM(D4:D14)/AVERAGE(E4:E14),0)</f>
         <v/>
       </c>
@@ -10234,7 +10399,7 @@
           <t>Forecast Accuracy %</t>
         </is>
       </c>
-      <c r="B21" s="98">
+      <c r="B21" s="100">
         <f>1-SUM(E4:E14)/SUM(C4:C14)</f>
         <v/>
       </c>
@@ -10249,7 +10414,7 @@
           <t>Mean Absolute Error (₹ Cr)</t>
         </is>
       </c>
-      <c r="B22" s="100">
+      <c r="B22" s="102">
         <f>AVERAGE(E4:E14)</f>
         <v/>
       </c>
@@ -10328,312 +10493,312 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="89" t="inlineStr">
+      <c r="A4" s="91" t="inlineStr">
         <is>
           <t>Apr'26</t>
         </is>
       </c>
-      <c r="B4" s="89" t="inlineStr">
+      <c r="B4" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C4" s="89" t="inlineStr">
+      <c r="C4" s="91" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="D4" s="101" t="n">
+      <c r="D4" s="103" t="n">
         <v>50.724</v>
       </c>
-      <c r="E4" s="102" t="inlineStr"/>
-      <c r="F4" s="103" t="inlineStr">
+      <c r="E4" s="104" t="inlineStr"/>
+      <c r="F4" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="89" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>May'26</t>
         </is>
       </c>
-      <c r="B5" s="89" t="inlineStr">
+      <c r="B5" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C5" s="89" t="inlineStr">
+      <c r="C5" s="91" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="D5" s="101" t="n">
+      <c r="D5" s="103" t="n">
         <v>38.0052</v>
       </c>
-      <c r="E5" s="102" t="inlineStr"/>
-      <c r="F5" s="103" t="inlineStr">
+      <c r="E5" s="104" t="inlineStr"/>
+      <c r="F5" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="89" t="inlineStr">
+      <c r="A6" s="91" t="inlineStr">
         <is>
           <t>Jun'26</t>
         </is>
       </c>
-      <c r="B6" s="89" t="inlineStr">
+      <c r="B6" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C6" s="89" t="inlineStr">
+      <c r="C6" s="91" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="D6" s="101" t="n">
+      <c r="D6" s="103" t="n">
         <v>36.2785</v>
       </c>
-      <c r="E6" s="102" t="inlineStr"/>
-      <c r="F6" s="103" t="inlineStr">
+      <c r="E6" s="104" t="inlineStr"/>
+      <c r="F6" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="89" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>Jul'26</t>
         </is>
       </c>
-      <c r="B7" s="89" t="inlineStr">
+      <c r="B7" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C7" s="89" t="inlineStr">
+      <c r="C7" s="91" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D7" s="101" t="n">
+      <c r="D7" s="103" t="n">
         <v>44.274</v>
       </c>
-      <c r="E7" s="102" t="inlineStr"/>
-      <c r="F7" s="103" t="inlineStr">
+      <c r="E7" s="104" t="inlineStr"/>
+      <c r="F7" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="89" t="inlineStr">
+      <c r="A8" s="91" t="inlineStr">
         <is>
           <t>Aug'26</t>
         </is>
       </c>
-      <c r="B8" s="89" t="inlineStr">
+      <c r="B8" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C8" s="89" t="inlineStr">
+      <c r="C8" s="91" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D8" s="101" t="n">
+      <c r="D8" s="103" t="n">
         <v>35.604</v>
       </c>
-      <c r="E8" s="102" t="inlineStr"/>
-      <c r="F8" s="103" t="inlineStr">
+      <c r="E8" s="104" t="inlineStr"/>
+      <c r="F8" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="89" t="inlineStr">
+      <c r="A9" s="91" t="inlineStr">
         <is>
           <t>Sep'26</t>
         </is>
       </c>
-      <c r="B9" s="89" t="inlineStr">
+      <c r="B9" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C9" s="89" t="inlineStr">
+      <c r="C9" s="91" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D9" s="101" t="n">
+      <c r="D9" s="103" t="n">
         <v>40.08</v>
       </c>
-      <c r="E9" s="102" t="inlineStr"/>
-      <c r="F9" s="103" t="inlineStr">
+      <c r="E9" s="104" t="inlineStr"/>
+      <c r="F9" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="89" t="inlineStr">
+      <c r="A10" s="91" t="inlineStr">
         <is>
           <t>Oct'26</t>
         </is>
       </c>
-      <c r="B10" s="89" t="inlineStr">
+      <c r="B10" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C10" s="89" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="D10" s="101" t="n">
+      <c r="D10" s="103" t="n">
         <v>30.0378</v>
       </c>
-      <c r="E10" s="102" t="inlineStr"/>
-      <c r="F10" s="103" t="inlineStr">
+      <c r="E10" s="104" t="inlineStr"/>
+      <c r="F10" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="89" t="inlineStr">
+      <c r="A11" s="91" t="inlineStr">
         <is>
           <t>Nov'26</t>
         </is>
       </c>
-      <c r="B11" s="89" t="inlineStr">
+      <c r="B11" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C11" s="89" t="inlineStr">
+      <c r="C11" s="91" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="D11" s="101" t="n">
+      <c r="D11" s="103" t="n">
         <v>36.9492</v>
       </c>
-      <c r="E11" s="102" t="inlineStr"/>
-      <c r="F11" s="103" t="inlineStr">
+      <c r="E11" s="104" t="inlineStr"/>
+      <c r="F11" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="89" t="inlineStr">
+      <c r="A12" s="91" t="inlineStr">
         <is>
           <t>Dec'26</t>
         </is>
       </c>
-      <c r="B12" s="89" t="inlineStr">
+      <c r="B12" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C12" s="89" t="inlineStr">
+      <c r="C12" s="91" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="D12" s="101" t="n">
+      <c r="D12" s="103" t="n">
         <v>30.9651</v>
       </c>
-      <c r="E12" s="102" t="inlineStr"/>
-      <c r="F12" s="103" t="inlineStr">
+      <c r="E12" s="104" t="inlineStr"/>
+      <c r="F12" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="89" t="inlineStr">
+      <c r="A13" s="91" t="inlineStr">
         <is>
           <t>Jan'27</t>
         </is>
       </c>
-      <c r="B13" s="89" t="inlineStr">
+      <c r="B13" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C13" s="89" t="inlineStr">
+      <c r="C13" s="91" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="D13" s="101" t="n">
+      <c r="D13" s="103" t="n">
         <v>35.9733</v>
       </c>
-      <c r="E13" s="102" t="inlineStr"/>
-      <c r="F13" s="103" t="inlineStr">
+      <c r="E13" s="104" t="inlineStr"/>
+      <c r="F13" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="89" t="inlineStr">
+      <c r="A14" s="91" t="inlineStr">
         <is>
           <t>Feb'27</t>
         </is>
       </c>
-      <c r="B14" s="89" t="inlineStr">
+      <c r="B14" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C14" s="89" t="inlineStr">
+      <c r="C14" s="91" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="D14" s="101" t="n">
+      <c r="D14" s="103" t="n">
         <v>28.3675</v>
       </c>
-      <c r="E14" s="102" t="inlineStr"/>
-      <c r="F14" s="103" t="inlineStr">
+      <c r="E14" s="104" t="inlineStr"/>
+      <c r="F14" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="89" t="inlineStr">
+      <c r="A15" s="91" t="inlineStr">
         <is>
           <t>Mar'27</t>
         </is>
       </c>
-      <c r="B15" s="89" t="inlineStr">
+      <c r="B15" s="91" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="C15" s="89" t="inlineStr">
+      <c r="C15" s="91" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="D15" s="101" t="n">
+      <c r="D15" s="103" t="n">
         <v>34.07</v>
       </c>
-      <c r="E15" s="102" t="inlineStr"/>
-      <c r="F15" s="103" t="inlineStr">
+      <c r="E15" s="104" t="inlineStr"/>
+      <c r="F15" s="105" t="inlineStr">
         <is>
           <t>editable</t>
         </is>
@@ -10782,46 +10947,46 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C4" s="104" t="n">
+      <c r="C4" s="106" t="n">
         <v>15.9007</v>
       </c>
-      <c r="D4" s="104" t="n">
+      <c r="D4" s="106" t="n">
         <v>11.4368</v>
       </c>
-      <c r="E4" s="104" t="n">
+      <c r="E4" s="106" t="n">
         <v>9.6591</v>
       </c>
-      <c r="F4" s="104" t="n">
+      <c r="F4" s="106" t="n">
         <v>9.8438</v>
       </c>
-      <c r="G4" s="104" t="n">
+      <c r="G4" s="106" t="n">
         <v>9.175700000000001</v>
       </c>
-      <c r="H4" s="104" t="n">
+      <c r="H4" s="106" t="n">
         <v>8.508699999999999</v>
       </c>
-      <c r="I4" s="104" t="n">
+      <c r="I4" s="106" t="n">
         <v>11.2423</v>
       </c>
-      <c r="J4" s="104" t="n">
+      <c r="J4" s="106" t="n">
         <v>11.9184</v>
       </c>
-      <c r="K4" s="104" t="n">
+      <c r="K4" s="106" t="n">
         <v>9.306900000000001</v>
       </c>
-      <c r="L4" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="104" t="n">
+      <c r="L4" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="106" t="n">
         <v>20.0498</v>
       </c>
-      <c r="P4" s="104" t="n">
+      <c r="P4" s="106" t="n">
         <v>15.2614</v>
       </c>
     </row>
@@ -10836,46 +11001,46 @@
           <t>Hair</t>
         </is>
       </c>
-      <c r="C5" s="104" t="n">
+      <c r="C5" s="106" t="n">
         <v>7.635</v>
       </c>
-      <c r="D5" s="104" t="n">
+      <c r="D5" s="106" t="n">
         <v>5.3597</v>
       </c>
-      <c r="E5" s="104" t="n">
+      <c r="E5" s="106" t="n">
         <v>5.8434</v>
       </c>
-      <c r="F5" s="104" t="n">
+      <c r="F5" s="106" t="n">
         <v>8.4824</v>
       </c>
-      <c r="G5" s="104" t="n">
+      <c r="G5" s="106" t="n">
         <v>5.9802</v>
       </c>
-      <c r="H5" s="104" t="n">
+      <c r="H5" s="106" t="n">
         <v>5.7138</v>
       </c>
-      <c r="I5" s="104" t="n">
+      <c r="I5" s="106" t="n">
         <v>6.03</v>
       </c>
-      <c r="J5" s="104" t="n">
+      <c r="J5" s="106" t="n">
         <v>7.1792</v>
       </c>
-      <c r="K5" s="104" t="n">
+      <c r="K5" s="106" t="n">
         <v>6.8971</v>
       </c>
-      <c r="L5" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="104" t="n">
+      <c r="L5" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="106" t="n">
         <v>9.3225</v>
       </c>
-      <c r="P5" s="104" t="n">
+      <c r="P5" s="106" t="n">
         <v>8.7301</v>
       </c>
     </row>
@@ -10890,46 +11055,46 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C6" s="104" t="n">
+      <c r="C6" s="106" t="n">
         <v>3.0148</v>
       </c>
-      <c r="D6" s="104" t="n">
+      <c r="D6" s="106" t="n">
         <v>2.4105</v>
       </c>
-      <c r="E6" s="104" t="n">
+      <c r="E6" s="106" t="n">
         <v>2.774</v>
       </c>
-      <c r="F6" s="104" t="n">
+      <c r="F6" s="106" t="n">
         <v>2.5041</v>
       </c>
-      <c r="G6" s="104" t="n">
+      <c r="G6" s="106" t="n">
         <v>2.5557</v>
       </c>
-      <c r="H6" s="104" t="n">
+      <c r="H6" s="106" t="n">
         <v>2.4714</v>
       </c>
-      <c r="I6" s="104" t="n">
+      <c r="I6" s="106" t="n">
         <v>2.5625</v>
       </c>
-      <c r="J6" s="104" t="n">
+      <c r="J6" s="106" t="n">
         <v>4.9955</v>
       </c>
-      <c r="K6" s="104" t="n">
+      <c r="K6" s="106" t="n">
         <v>5.8649</v>
       </c>
-      <c r="L6" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="104" t="n">
+      <c r="L6" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="106" t="n">
         <v>15.9714</v>
       </c>
-      <c r="P6" s="104" t="n">
+      <c r="P6" s="106" t="n">
         <v>14.0662</v>
       </c>
     </row>
@@ -10944,46 +11109,46 @@
           <t>Body</t>
         </is>
       </c>
-      <c r="C7" s="104" t="n">
+      <c r="C7" s="106" t="n">
         <v>1.809</v>
       </c>
-      <c r="D7" s="104" t="n">
+      <c r="D7" s="106" t="n">
         <v>1.1083</v>
       </c>
-      <c r="E7" s="104" t="n">
+      <c r="E7" s="106" t="n">
         <v>0.831</v>
       </c>
-      <c r="F7" s="104" t="n">
+      <c r="F7" s="106" t="n">
         <v>1.1064</v>
       </c>
-      <c r="G7" s="104" t="n">
+      <c r="G7" s="106" t="n">
         <v>1.937</v>
       </c>
-      <c r="H7" s="104" t="n">
+      <c r="H7" s="106" t="n">
         <v>3.3743</v>
       </c>
-      <c r="I7" s="104" t="n">
+      <c r="I7" s="106" t="n">
         <v>4.5195</v>
       </c>
-      <c r="J7" s="104" t="n">
+      <c r="J7" s="106" t="n">
         <v>5.9683</v>
       </c>
-      <c r="K7" s="104" t="n">
+      <c r="K7" s="106" t="n">
         <v>4.055</v>
       </c>
-      <c r="L7" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="104" t="n">
+      <c r="L7" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="106" t="n">
         <v>1.7566</v>
       </c>
-      <c r="P7" s="104" t="n">
+      <c r="P7" s="106" t="n">
         <v>2.1697</v>
       </c>
     </row>
@@ -10998,46 +11163,46 @@
           <t>Baby</t>
         </is>
       </c>
-      <c r="C8" s="104" t="n">
+      <c r="C8" s="106" t="n">
         <v>2.1443</v>
       </c>
-      <c r="D8" s="104" t="n">
+      <c r="D8" s="106" t="n">
         <v>2.5588</v>
       </c>
-      <c r="E8" s="104" t="n">
+      <c r="E8" s="106" t="n">
         <v>2.1482</v>
       </c>
-      <c r="F8" s="104" t="n">
+      <c r="F8" s="106" t="n">
         <v>2.1917</v>
       </c>
-      <c r="G8" s="104" t="n">
+      <c r="G8" s="106" t="n">
         <v>1.7488</v>
       </c>
-      <c r="H8" s="104" t="n">
+      <c r="H8" s="106" t="n">
         <v>1.7735</v>
       </c>
-      <c r="I8" s="104" t="n">
+      <c r="I8" s="106" t="n">
         <v>1.887</v>
       </c>
-      <c r="J8" s="104" t="n">
+      <c r="J8" s="106" t="n">
         <v>2.6584</v>
       </c>
-      <c r="K8" s="104" t="n">
+      <c r="K8" s="106" t="n">
         <v>1.8071</v>
       </c>
-      <c r="L8" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="104" t="n">
+      <c r="L8" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="106" t="n">
         <v>2.4517</v>
       </c>
-      <c r="P8" s="104" t="n">
+      <c r="P8" s="106" t="n">
         <v>2.2008</v>
       </c>
     </row>
@@ -11052,46 +11217,46 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C9" s="104" t="n">
+      <c r="C9" s="106" t="n">
         <v>0.8697</v>
       </c>
-      <c r="D9" s="104" t="n">
+      <c r="D9" s="106" t="n">
         <v>0.5691000000000001</v>
       </c>
-      <c r="E9" s="104" t="n">
+      <c r="E9" s="106" t="n">
         <v>0.3599</v>
       </c>
-      <c r="F9" s="104" t="n">
+      <c r="F9" s="106" t="n">
         <v>0.3573</v>
       </c>
-      <c r="G9" s="104" t="n">
+      <c r="G9" s="106" t="n">
         <v>0.2789</v>
       </c>
-      <c r="H9" s="104" t="n">
+      <c r="H9" s="106" t="n">
         <v>0.2944</v>
       </c>
-      <c r="I9" s="104" t="n">
+      <c r="I9" s="106" t="n">
         <v>0.3455</v>
       </c>
-      <c r="J9" s="104" t="n">
+      <c r="J9" s="106" t="n">
         <v>0.3634</v>
       </c>
-      <c r="K9" s="104" t="n">
+      <c r="K9" s="106" t="n">
         <v>0.3811</v>
       </c>
-      <c r="L9" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="104" t="n">
+      <c r="L9" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="106" t="n">
         <v>1.0469</v>
       </c>
-      <c r="P9" s="104" t="n">
+      <c r="P9" s="106" t="n">
         <v>1.4269</v>
       </c>
     </row>
@@ -11106,46 +11271,46 @@
           <t>Hair Care</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
+      <c r="C10" s="106" t="n">
         <v>0.0621</v>
       </c>
-      <c r="D10" s="104" t="n">
+      <c r="D10" s="106" t="n">
         <v>0.055</v>
       </c>
-      <c r="E10" s="104" t="n">
+      <c r="E10" s="106" t="n">
         <v>0.0529</v>
       </c>
-      <c r="F10" s="104" t="n">
+      <c r="F10" s="106" t="n">
         <v>0.0759</v>
       </c>
-      <c r="G10" s="104" t="n">
+      <c r="G10" s="106" t="n">
         <v>0.0202</v>
       </c>
-      <c r="H10" s="104" t="n">
+      <c r="H10" s="106" t="n">
         <v>0.0843</v>
       </c>
-      <c r="I10" s="104" t="n">
+      <c r="I10" s="106" t="n">
         <v>0.021</v>
       </c>
-      <c r="J10" s="104" t="n">
+      <c r="J10" s="106" t="n">
         <v>0.0521</v>
       </c>
-      <c r="K10" s="104" t="n">
+      <c r="K10" s="106" t="n">
         <v>0.0081</v>
       </c>
-      <c r="L10" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="104" t="n">
+      <c r="L10" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="106" t="n">
         <v>0.0215</v>
       </c>
-      <c r="P10" s="104" t="n">
+      <c r="P10" s="106" t="n">
         <v>0.008999999999999999</v>
       </c>
     </row>
@@ -11160,46 +11325,46 @@
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="C11" s="104" t="n">
+      <c r="C11" s="106" t="n">
         <v>0.2338</v>
       </c>
-      <c r="D11" s="104" t="n">
+      <c r="D11" s="106" t="n">
         <v>0.1379</v>
       </c>
-      <c r="E11" s="104" t="n">
+      <c r="E11" s="106" t="n">
         <v>0.0337</v>
       </c>
-      <c r="F11" s="104" t="n">
+      <c r="F11" s="106" t="n">
         <v>0.0547</v>
       </c>
-      <c r="G11" s="104" t="n">
+      <c r="G11" s="106" t="n">
         <v>0.0007</v>
       </c>
-      <c r="H11" s="104" t="n">
+      <c r="H11" s="106" t="n">
         <v>0.0003</v>
       </c>
-      <c r="I11" s="104" t="n">
+      <c r="I11" s="106" t="n">
         <v>-0.0039</v>
       </c>
-      <c r="J11" s="104" t="n">
+      <c r="J11" s="106" t="n">
         <v>-0.0067</v>
       </c>
-      <c r="K11" s="104" t="n">
+      <c r="K11" s="106" t="n">
         <v>-0.0291</v>
       </c>
-      <c r="L11" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="104" t="n">
+      <c r="L11" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="106" t="n">
         <v>-0.0051</v>
       </c>
-      <c r="P11" s="104" t="n">
+      <c r="P11" s="106" t="n">
         <v>-0.0001</v>
       </c>
     </row>
@@ -11214,46 +11379,46 @@
           <t>Styling Products</t>
         </is>
       </c>
-      <c r="C12" s="104" t="n">
+      <c r="C12" s="106" t="n">
         <v>0.0192</v>
       </c>
-      <c r="D12" s="104" t="n">
+      <c r="D12" s="106" t="n">
         <v>0.0154</v>
       </c>
-      <c r="E12" s="104" t="n">
+      <c r="E12" s="106" t="n">
         <v>0.0415</v>
       </c>
-      <c r="F12" s="104" t="n">
+      <c r="F12" s="106" t="n">
         <v>0.0528</v>
       </c>
-      <c r="G12" s="104" t="n">
+      <c r="G12" s="106" t="n">
         <v>0.0228</v>
       </c>
-      <c r="H12" s="104" t="n">
+      <c r="H12" s="106" t="n">
         <v>0.0144</v>
       </c>
-      <c r="I12" s="104" t="n">
+      <c r="I12" s="106" t="n">
         <v>0.0176</v>
       </c>
-      <c r="J12" s="104" t="n">
+      <c r="J12" s="106" t="n">
         <v>0.038</v>
       </c>
-      <c r="K12" s="104" t="n">
+      <c r="K12" s="106" t="n">
         <v>0.0196</v>
       </c>
-      <c r="L12" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="104" t="n">
+      <c r="L12" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="106" t="n">
         <v>0.0309</v>
       </c>
-      <c r="P12" s="104" t="n">
+      <c r="P12" s="106" t="n">
         <v>0.0319</v>
       </c>
     </row>
@@ -11268,46 +11433,46 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="104" t="n">
+      <c r="C13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="106" t="n">
         <v>0.0048</v>
       </c>
-      <c r="I13" s="104" t="n">
+      <c r="I13" s="106" t="n">
         <v>0.0597</v>
       </c>
-      <c r="J13" s="104" t="n">
+      <c r="J13" s="106" t="n">
         <v>0.0756</v>
       </c>
-      <c r="K13" s="104" t="n">
+      <c r="K13" s="106" t="n">
         <v>0.0317</v>
       </c>
-      <c r="L13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="104" t="n">
+      <c r="L13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="106" t="n">
         <v>0.0689</v>
       </c>
-      <c r="P13" s="104" t="n">
+      <c r="P13" s="106" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -11322,46 +11487,46 @@
           <t>Hair Colour</t>
         </is>
       </c>
-      <c r="C14" s="104" t="n">
+      <c r="C14" s="106" t="n">
         <v>0.0298</v>
       </c>
-      <c r="D14" s="104" t="n">
+      <c r="D14" s="106" t="n">
         <v>0.0327</v>
       </c>
-      <c r="E14" s="104" t="n">
+      <c r="E14" s="106" t="n">
         <v>0.0268</v>
       </c>
-      <c r="F14" s="104" t="n">
+      <c r="F14" s="106" t="n">
         <v>0.031</v>
       </c>
-      <c r="G14" s="104" t="n">
+      <c r="G14" s="106" t="n">
         <v>0.0015</v>
       </c>
-      <c r="H14" s="104" t="n">
+      <c r="H14" s="106" t="n">
         <v>-0.0041</v>
       </c>
-      <c r="I14" s="104" t="n">
+      <c r="I14" s="106" t="n">
         <v>0.0086</v>
       </c>
-      <c r="J14" s="104" t="n">
+      <c r="J14" s="106" t="n">
         <v>0.0183</v>
       </c>
-      <c r="K14" s="104" t="n">
+      <c r="K14" s="106" t="n">
         <v>-0.0049</v>
       </c>
-      <c r="L14" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="104" t="n">
+      <c r="L14" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="106" t="n">
         <v>0.0137</v>
       </c>
-      <c r="P14" s="104" t="n">
+      <c r="P14" s="106" t="n">
         <v>0.0282</v>
       </c>
     </row>
@@ -11376,46 +11541,46 @@
           <t>Fragrance</t>
         </is>
       </c>
-      <c r="C15" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="104" t="n">
+      <c r="C15" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="106" t="n">
         <v>0.0028</v>
       </c>
-      <c r="F15" s="104" t="n">
+      <c r="F15" s="106" t="n">
         <v>0.0065</v>
       </c>
-      <c r="G15" s="104" t="n">
+      <c r="G15" s="106" t="n">
         <v>0.0026</v>
       </c>
-      <c r="H15" s="104" t="n">
+      <c r="H15" s="106" t="n">
         <v>0.0046</v>
       </c>
-      <c r="I15" s="104" t="n">
+      <c r="I15" s="106" t="n">
         <v>0.0518</v>
       </c>
-      <c r="J15" s="104" t="n">
+      <c r="J15" s="106" t="n">
         <v>0.0065</v>
       </c>
-      <c r="K15" s="104" t="n">
+      <c r="K15" s="106" t="n">
         <v>0.0059</v>
       </c>
-      <c r="L15" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="104" t="n">
+      <c r="L15" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="106" t="n">
         <v>0.0008</v>
       </c>
-      <c r="P15" s="104" t="n">
+      <c r="P15" s="106" t="n">
         <v>0.0402</v>
       </c>
     </row>
@@ -11430,46 +11595,46 @@
           <t>Body</t>
         </is>
       </c>
-      <c r="C16" s="104" t="n">
+      <c r="C16" s="106" t="n">
         <v>0.0051</v>
       </c>
-      <c r="D16" s="104" t="n">
+      <c r="D16" s="106" t="n">
         <v>0.0018</v>
       </c>
-      <c r="E16" s="104" t="n">
+      <c r="E16" s="106" t="n">
         <v>0.0052</v>
       </c>
-      <c r="F16" s="104" t="n">
+      <c r="F16" s="106" t="n">
         <v>0.008699999999999999</v>
       </c>
-      <c r="G16" s="104" t="n">
+      <c r="G16" s="106" t="n">
         <v>0.0034</v>
       </c>
-      <c r="H16" s="104" t="n">
+      <c r="H16" s="106" t="n">
         <v>0.0097</v>
       </c>
-      <c r="I16" s="104" t="n">
+      <c r="I16" s="106" t="n">
         <v>-0.0023</v>
       </c>
-      <c r="J16" s="104" t="n">
+      <c r="J16" s="106" t="n">
         <v>0.0244</v>
       </c>
-      <c r="K16" s="104" t="n">
+      <c r="K16" s="106" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="L16" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="104" t="n">
+      <c r="L16" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="106" t="n">
         <v>0.009299999999999999</v>
       </c>
-      <c r="P16" s="104" t="n">
+      <c r="P16" s="106" t="n">
         <v>0.0345</v>
       </c>
     </row>
@@ -11484,46 +11649,46 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="104" t="n">
+      <c r="C17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="106" t="n">
         <v>0.0769</v>
       </c>
-      <c r="P17" s="104" t="n">
+      <c r="P17" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11538,46 +11703,46 @@
           <t>Hair</t>
         </is>
       </c>
-      <c r="C18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="104" t="n">
+      <c r="C18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="106" t="n">
         <v>-0</v>
       </c>
-      <c r="H18" s="104" t="n">
+      <c r="H18" s="106" t="n">
         <v>0.0123</v>
       </c>
-      <c r="I18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="104" t="n">
+      <c r="I18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="106" t="n">
         <v>-0.0002</v>
       </c>
-      <c r="L18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="104" t="n">
+      <c r="L18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="106" t="n">
         <v>0.0097</v>
       </c>
-      <c r="P18" s="104" t="n">
+      <c r="P18" s="106" t="n">
         <v>0.0434</v>
       </c>
     </row>
@@ -11592,46 +11757,46 @@
           <t>Combo</t>
         </is>
       </c>
-      <c r="C19" s="104" t="n">
+      <c r="C19" s="106" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="D19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="104" t="n">
+      <c r="D19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="106" t="n">
         <v>0.0631</v>
       </c>
     </row>
@@ -11646,46 +11811,46 @@
           <t>Lip</t>
         </is>
       </c>
-      <c r="C20" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="104" t="n">
+      <c r="C20" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="106" t="n">
         <v>0.0003</v>
       </c>
-      <c r="E20" s="104" t="n">
+      <c r="E20" s="106" t="n">
         <v>0.0235</v>
       </c>
-      <c r="F20" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="104" t="n">
+      <c r="F20" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="106" t="n">
         <v>0.01</v>
       </c>
-      <c r="H20" s="104" t="n">
+      <c r="H20" s="106" t="n">
         <v>0.0053</v>
       </c>
-      <c r="I20" s="104" t="n">
+      <c r="I20" s="106" t="n">
         <v>0.0062</v>
       </c>
-      <c r="J20" s="104" t="n">
+      <c r="J20" s="106" t="n">
         <v>0.0059</v>
       </c>
-      <c r="K20" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="104" t="n">
+      <c r="K20" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11700,46 +11865,46 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C21" s="104" t="n">
+      <c r="C21" s="106" t="n">
         <v>0.02</v>
       </c>
-      <c r="D21" s="104" t="n">
+      <c r="D21" s="106" t="n">
         <v>0.0217</v>
       </c>
-      <c r="E21" s="104" t="n">
+      <c r="E21" s="106" t="n">
         <v>0.0038</v>
       </c>
-      <c r="F21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="104" t="n">
+      <c r="F21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="106" t="n">
         <v>-0.0032</v>
       </c>
     </row>
@@ -11754,46 +11919,46 @@
           <t>Combo</t>
         </is>
       </c>
-      <c r="C22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="104" t="n">
+      <c r="C22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="106" t="n">
         <v>0.008699999999999999</v>
       </c>
     </row>
@@ -11808,46 +11973,46 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="104" t="n">
+      <c r="C23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="106" t="n">
         <v>0.003</v>
       </c>
-      <c r="F23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="104" t="n">
+      <c r="F23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="106" t="n">
         <v>0.0003</v>
       </c>
-      <c r="H23" s="104" t="n">
+      <c r="H23" s="106" t="n">
         <v>0.0016</v>
       </c>
-      <c r="I23" s="104" t="n">
+      <c r="I23" s="106" t="n">
         <v>0.0016</v>
       </c>
-      <c r="J23" s="104" t="n">
+      <c r="J23" s="106" t="n">
         <v>0.0003</v>
       </c>
-      <c r="K23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="104" t="n">
+      <c r="K23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11862,46 +12027,46 @@
           <t>Eye</t>
         </is>
       </c>
-      <c r="C24" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="104" t="n">
+      <c r="C24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="106" t="n">
         <v>0.0002</v>
       </c>
-      <c r="E24" s="104" t="n">
+      <c r="E24" s="106" t="n">
         <v>0.0012</v>
       </c>
-      <c r="F24" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="104" t="n">
+      <c r="F24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="106" t="n">
         <v>0.0002</v>
       </c>
-      <c r="H24" s="104" t="n">
+      <c r="H24" s="106" t="n">
         <v>0.0009</v>
       </c>
-      <c r="I24" s="104" t="n">
+      <c r="I24" s="106" t="n">
         <v>0.0009</v>
       </c>
-      <c r="J24" s="104" t="n">
+      <c r="J24" s="106" t="n">
         <v>0.0005</v>
       </c>
-      <c r="K24" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="104" t="n">
+      <c r="K24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11916,46 +12081,46 @@
           <t>Color Care</t>
         </is>
       </c>
-      <c r="C25" s="104" t="n">
+      <c r="C25" s="106" t="n">
         <v>0.0018</v>
       </c>
-      <c r="D25" s="104" t="n">
+      <c r="D25" s="106" t="n">
         <v>0.0015</v>
       </c>
-      <c r="E25" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="104" t="n">
+      <c r="E25" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="106" t="n">
         <v>0.0022</v>
       </c>
-      <c r="G25" s="104" t="n">
+      <c r="G25" s="106" t="n">
         <v>-0.0002</v>
       </c>
-      <c r="H25" s="104" t="n">
+      <c r="H25" s="106" t="n">
         <v>-0.002</v>
       </c>
-      <c r="I25" s="104" t="n">
+      <c r="I25" s="106" t="n">
         <v>-0.0016</v>
       </c>
-      <c r="J25" s="104" t="n">
+      <c r="J25" s="106" t="n">
         <v>0.0042</v>
       </c>
-      <c r="K25" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="104" t="n">
+      <c r="K25" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="106" t="n">
         <v>-0.0026</v>
       </c>
-      <c r="P25" s="104" t="n">
+      <c r="P25" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11970,46 +12135,46 @@
           <t>Body</t>
         </is>
       </c>
-      <c r="C26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="104" t="n">
+      <c r="C26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="106" t="n">
         <v>0.001</v>
       </c>
-      <c r="L26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="104" t="n">
+      <c r="L26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="106" t="n">
         <v>0.0021</v>
       </c>
-      <c r="P26" s="104" t="n">
+      <c r="P26" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12024,46 +12189,46 @@
           <t>Personal Care</t>
         </is>
       </c>
-      <c r="C27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="104" t="n">
+      <c r="C27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="106" t="n">
         <v>0.0012</v>
       </c>
-      <c r="I27" s="104" t="n">
+      <c r="I27" s="106" t="n">
         <v>0.0012</v>
       </c>
-      <c r="J27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="104" t="n">
+      <c r="J27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12078,46 +12243,46 @@
           <t>Makeup Combo</t>
         </is>
       </c>
-      <c r="C28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="104" t="n">
+      <c r="C28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="106" t="n">
         <v>0.0015</v>
       </c>
-      <c r="K28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="104" t="n">
+      <c r="K28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12132,46 +12297,46 @@
           <t>Salon Secret</t>
         </is>
       </c>
-      <c r="C29" s="104" t="n">
+      <c r="C29" s="106" t="n">
         <v>-0.0002</v>
       </c>
-      <c r="D29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="104" t="n">
+      <c r="D29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="106" t="n">
         <v>-0.001</v>
       </c>
-      <c r="H29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="104" t="n">
+      <c r="H29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12186,46 +12351,46 @@
           <t>Premium Range</t>
         </is>
       </c>
-      <c r="C30" s="104" t="n">
+      <c r="C30" s="106" t="n">
         <v>-0.0002</v>
       </c>
-      <c r="D30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="104" t="n">
+      <c r="D30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="106" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="H30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="104" t="n">
+      <c r="H30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="106" t="n">
         <v>-0.0004</v>
       </c>
-      <c r="K30" s="104" t="n">
+      <c r="K30" s="106" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="L30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="104" t="n">
+      <c r="L30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12240,46 +12405,46 @@
           <t>Lip</t>
         </is>
       </c>
-      <c r="C31" s="104" t="n">
+      <c r="C31" s="106" t="n">
         <v>-0.0014</v>
       </c>
-      <c r="D31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="104" t="n">
+      <c r="D31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="106" t="n">
         <v>0.0003</v>
       </c>
-      <c r="F31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="104" t="n">
+      <c r="F31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="106" t="n">
         <v>-0.0002</v>
       </c>
-      <c r="H31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="104" t="n">
+      <c r="H31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="106" t="n">
         <v>-0.0002</v>
       </c>
-      <c r="L31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="104" t="n">
+      <c r="L31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12294,46 +12459,46 @@
           <t>Body</t>
         </is>
       </c>
-      <c r="C32" s="104" t="n">
+      <c r="C32" s="106" t="n">
         <v>-0.0008</v>
       </c>
-      <c r="D32" s="104" t="n">
+      <c r="D32" s="106" t="n">
         <v>0.0002</v>
       </c>
-      <c r="E32" s="104" t="n">
+      <c r="E32" s="106" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="F32" s="104" t="n">
+      <c r="F32" s="106" t="n">
         <v>0.0002</v>
       </c>
-      <c r="G32" s="104" t="n">
+      <c r="G32" s="106" t="n">
         <v>-0.0005</v>
       </c>
-      <c r="H32" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="104" t="n">
+      <c r="H32" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="106" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="K32" s="104" t="n">
+      <c r="K32" s="106" t="n">
         <v>-0.0001</v>
       </c>
-      <c r="L32" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="104" t="n">
+      <c r="L32" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12348,109 +12513,109 @@
           <t>Color Care</t>
         </is>
       </c>
-      <c r="C33" s="104" t="n">
+      <c r="C33" s="106" t="n">
         <v>0.0035</v>
       </c>
-      <c r="D33" s="104" t="n">
+      <c r="D33" s="106" t="n">
         <v>-0.0408</v>
       </c>
-      <c r="E33" s="104" t="n">
+      <c r="E33" s="106" t="n">
         <v>0.0165</v>
       </c>
-      <c r="F33" s="104" t="n">
+      <c r="F33" s="106" t="n">
         <v>0.0114</v>
       </c>
-      <c r="G33" s="104" t="n">
+      <c r="G33" s="106" t="n">
         <v>-0.1117</v>
       </c>
-      <c r="H33" s="104" t="n">
+      <c r="H33" s="106" t="n">
         <v>-0.032</v>
       </c>
-      <c r="I33" s="104" t="n">
+      <c r="I33" s="106" t="n">
         <v>0.0012</v>
       </c>
-      <c r="J33" s="104" t="n">
+      <c r="J33" s="106" t="n">
         <v>-0.0097</v>
       </c>
-      <c r="K33" s="104" t="n">
+      <c r="K33" s="106" t="n">
         <v>-0.1468</v>
       </c>
-      <c r="L33" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="104" t="n">
+      <c r="L33" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="106" t="n">
         <v>-0.0564</v>
       </c>
-      <c r="P33" s="104" t="n">
+      <c r="P33" s="106" t="n">
         <v>0.0236</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="105" t="inlineStr">
+      <c r="A34" s="107" t="inlineStr">
         <is>
           <t>COMPANY TOTAL</t>
         </is>
       </c>
-      <c r="B34" s="105" t="inlineStr"/>
-      <c r="C34" s="106">
+      <c r="B34" s="107" t="inlineStr"/>
+      <c r="C34" s="108">
         <f>SUM(C4:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="106">
+      <c r="D34" s="108">
         <f>SUM(D4:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="106">
+      <c r="E34" s="108">
         <f>SUM(E4:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="106">
+      <c r="F34" s="108">
         <f>SUM(F4:F33)</f>
         <v/>
       </c>
-      <c r="G34" s="106">
+      <c r="G34" s="108">
         <f>SUM(G4:G33)</f>
         <v/>
       </c>
-      <c r="H34" s="106">
+      <c r="H34" s="108">
         <f>SUM(H4:H33)</f>
         <v/>
       </c>
-      <c r="I34" s="106">
+      <c r="I34" s="108">
         <f>SUM(I4:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="106">
+      <c r="J34" s="108">
         <f>SUM(J4:J33)</f>
         <v/>
       </c>
-      <c r="K34" s="106">
+      <c r="K34" s="108">
         <f>SUM(K4:K33)</f>
         <v/>
       </c>
-      <c r="L34" s="106">
+      <c r="L34" s="108">
         <f>SUM(L4:L33)</f>
         <v/>
       </c>
-      <c r="M34" s="106">
+      <c r="M34" s="108">
         <f>SUM(M4:M33)</f>
         <v/>
       </c>
-      <c r="N34" s="106">
+      <c r="N34" s="108">
         <f>SUM(N4:N33)</f>
         <v/>
       </c>
-      <c r="O34" s="106">
+      <c r="O34" s="108">
         <f>SUM(O4:O33)</f>
         <v/>
       </c>
-      <c r="P34" s="106">
+      <c r="P34" s="108">
         <f>SUM(P4:P33)</f>
         <v/>
       </c>
@@ -12532,13 +12697,13 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C4" s="104" t="n">
+      <c r="C4" s="106" t="n">
         <v>26.6306</v>
       </c>
-      <c r="D4" s="104" t="n">
+      <c r="D4" s="106" t="n">
         <v>44.0883</v>
       </c>
-      <c r="E4" s="107">
+      <c r="E4" s="109">
         <f>D4</f>
         <v/>
       </c>
@@ -12554,13 +12719,13 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C5" s="104" t="n">
+      <c r="C5" s="106" t="n">
         <v>18.3728</v>
       </c>
-      <c r="D5" s="104" t="n">
+      <c r="D5" s="106" t="n">
         <v>26.2195</v>
       </c>
-      <c r="E5" s="107">
+      <c r="E5" s="109">
         <f>D5</f>
         <v/>
       </c>
@@ -12576,13 +12741,13 @@
           <t>Hair</t>
         </is>
       </c>
-      <c r="C6" s="104" t="n">
+      <c r="C6" s="106" t="n">
         <v>10.4807</v>
       </c>
-      <c r="D6" s="104" t="n">
+      <c r="D6" s="106" t="n">
         <v>24.1948</v>
       </c>
-      <c r="E6" s="107">
+      <c r="E6" s="109">
         <f>D6</f>
         <v/>
       </c>
@@ -12598,13 +12763,13 @@
           <t>Body</t>
         </is>
       </c>
-      <c r="C7" s="104" t="n">
+      <c r="C7" s="106" t="n">
         <v>3.9288</v>
       </c>
-      <c r="D7" s="104" t="n">
+      <c r="D7" s="106" t="n">
         <v>6.2024</v>
       </c>
-      <c r="E7" s="107">
+      <c r="E7" s="109">
         <f>D7</f>
         <v/>
       </c>
@@ -12620,13 +12785,13 @@
           <t>Baby</t>
         </is>
       </c>
-      <c r="C8" s="104" t="n">
+      <c r="C8" s="106" t="n">
         <v>3.4349</v>
       </c>
-      <c r="D8" s="104" t="n">
+      <c r="D8" s="106" t="n">
         <v>4.452</v>
       </c>
-      <c r="E8" s="107">
+      <c r="E8" s="109">
         <f>D8</f>
         <v/>
       </c>
@@ -12642,13 +12807,13 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C9" s="104" t="n">
+      <c r="C9" s="106" t="n">
         <v>0.7524999999999999</v>
       </c>
-      <c r="D9" s="104" t="n">
+      <c r="D9" s="106" t="n">
         <v>1.4376</v>
       </c>
-      <c r="E9" s="107">
+      <c r="E9" s="109">
         <f>D9</f>
         <v/>
       </c>
@@ -12664,13 +12829,13 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n">
+      <c r="C10" s="106" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="D10" s="104" t="n">
+      <c r="D10" s="106" t="n">
         <v>0.08260000000000001</v>
       </c>
-      <c r="E10" s="107">
+      <c r="E10" s="109">
         <f>D10</f>
         <v/>
       </c>
@@ -12686,13 +12851,13 @@
           <t>Styling Products</t>
         </is>
       </c>
-      <c r="C11" s="104" t="n">
+      <c r="C11" s="106" t="n">
         <v>0.0519</v>
       </c>
-      <c r="D11" s="104" t="n">
+      <c r="D11" s="106" t="n">
         <v>0.0522</v>
       </c>
-      <c r="E11" s="107">
+      <c r="E11" s="109">
         <f>D11</f>
         <v/>
       </c>
@@ -12708,13 +12873,13 @@
           <t>Hair Care</t>
         </is>
       </c>
-      <c r="C12" s="104" t="n">
+      <c r="C12" s="106" t="n">
         <v>0.0233</v>
       </c>
-      <c r="D12" s="104" t="n">
+      <c r="D12" s="106" t="n">
         <v>0.0683</v>
       </c>
-      <c r="E12" s="107">
+      <c r="E12" s="109">
         <f>D12</f>
         <v/>
       </c>
@@ -12730,13 +12895,13 @@
           <t>Color Care</t>
         </is>
       </c>
-      <c r="C13" s="104" t="n">
+      <c r="C13" s="106" t="n">
         <v>0.0233</v>
       </c>
-      <c r="D13" s="104" t="n">
+      <c r="D13" s="106" t="n">
         <v>0.0409</v>
       </c>
-      <c r="E13" s="107">
+      <c r="E13" s="109">
         <f>D13</f>
         <v/>
       </c>
@@ -12752,13 +12917,13 @@
           <t>Hair</t>
         </is>
       </c>
-      <c r="C14" s="104" t="n">
+      <c r="C14" s="106" t="n">
         <v>0.0217</v>
       </c>
-      <c r="D14" s="104" t="n">
+      <c r="D14" s="106" t="n">
         <v>0.0275</v>
       </c>
-      <c r="E14" s="107">
+      <c r="E14" s="109">
         <f>D14</f>
         <v/>
       </c>
@@ -12774,13 +12939,13 @@
           <t>Hair Colour</t>
         </is>
       </c>
-      <c r="C15" s="104" t="n">
+      <c r="C15" s="106" t="n">
         <v>0.0209</v>
       </c>
-      <c r="D15" s="104" t="n">
+      <c r="D15" s="106" t="n">
         <v>0.0277</v>
       </c>
-      <c r="E15" s="107">
+      <c r="E15" s="109">
         <f>D15</f>
         <v/>
       </c>
@@ -12796,13 +12961,13 @@
           <t>Body</t>
         </is>
       </c>
-      <c r="C16" s="104" t="n">
+      <c r="C16" s="106" t="n">
         <v>0.0136</v>
       </c>
-      <c r="D16" s="104" t="n">
+      <c r="D16" s="106" t="n">
         <v>0.0246</v>
       </c>
-      <c r="E16" s="107">
+      <c r="E16" s="109">
         <f>D16</f>
         <v/>
       </c>
@@ -12818,13 +12983,13 @@
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="C17" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="104" t="n">
+      <c r="C17" s="106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="106" t="n">
         <v>0.0152</v>
       </c>
-      <c r="E17" s="107">
+      <c r="E17" s="109">
         <f>D17</f>
         <v/>
       </c>
@@ -12937,38 +13102,38 @@
           <t>Avenue Supermarts Ltd.-DC-1039</t>
         </is>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="96" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="96" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="D4" s="104" t="n">
+      <c r="D4" s="106" t="n">
         <v>18.184</v>
       </c>
-      <c r="E4" s="108" t="n">
+      <c r="E4" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="108" t="n">
+      <c r="F4" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G4" s="108" t="n">
+      <c r="G4" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H4" s="109" t="n">
+      <c r="H4" s="111" t="n">
         <v>0.95</v>
       </c>
-      <c r="I4" s="109" t="n">
+      <c r="I4" s="111" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J4" s="108" t="n">
+      <c r="J4" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K4" s="109" t="n">
+      <c r="K4" s="111" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -12978,38 +13143,38 @@
           <t>Sri Vijaya Durga Agencies_Mt</t>
         </is>
       </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="96" t="inlineStr">
         <is>
           <t>South-2</t>
         </is>
       </c>
-      <c r="D5" s="104" t="n">
+      <c r="D5" s="106" t="n">
         <v>16.852</v>
       </c>
-      <c r="E5" s="108" t="n">
+      <c r="E5" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="108" t="n">
+      <c r="F5" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G5" s="108" t="n">
+      <c r="G5" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H5" s="109" t="n">
+      <c r="H5" s="111" t="n">
         <v>0.88</v>
       </c>
-      <c r="I5" s="109" t="n">
+      <c r="I5" s="111" t="n">
         <v>0.88</v>
       </c>
-      <c r="J5" s="108" t="n">
+      <c r="J5" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K5" s="109" t="n">
+      <c r="K5" s="111" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -13019,38 +13184,38 @@
           <t>JUST MARK-Dmart_ship to</t>
         </is>
       </c>
-      <c r="B6" s="94" t="inlineStr">
+      <c r="B6" s="96" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="96" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="D6" s="104" t="n">
+      <c r="D6" s="106" t="n">
         <v>15.772</v>
       </c>
-      <c r="E6" s="108" t="n">
+      <c r="E6" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="108" t="n">
+      <c r="F6" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G6" s="108" t="n">
+      <c r="G6" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H6" s="109" t="n">
+      <c r="H6" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="I6" s="109" t="n">
+      <c r="I6" s="111" t="n">
         <v>0.84</v>
       </c>
-      <c r="J6" s="108" t="n">
+      <c r="J6" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="109" t="n">
+      <c r="K6" s="111" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -13060,38 +13225,38 @@
           <t>G.V Enterprises</t>
         </is>
       </c>
-      <c r="B7" s="94" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C7" s="94" t="inlineStr">
+      <c r="C7" s="96" t="inlineStr">
         <is>
           <t>South-1</t>
         </is>
       </c>
-      <c r="D7" s="104" t="n">
+      <c r="D7" s="106" t="n">
         <v>13.791</v>
       </c>
-      <c r="E7" s="108" t="n">
+      <c r="E7" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="108" t="n">
+      <c r="F7" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G7" s="108" t="n">
+      <c r="G7" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H7" s="109" t="n">
+      <c r="H7" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="I7" s="109" t="n">
+      <c r="I7" s="111" t="n">
         <v>0.95</v>
       </c>
-      <c r="J7" s="108" t="n">
+      <c r="J7" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K7" s="109" t="n">
+      <c r="K7" s="111" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -13101,38 +13266,38 @@
           <t>Avenue Supermarts Ltd.-DC-1032</t>
         </is>
       </c>
-      <c r="B8" s="94" t="inlineStr">
+      <c r="B8" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="96" t="inlineStr">
         <is>
           <t>South-1</t>
         </is>
       </c>
-      <c r="D8" s="104" t="n">
+      <c r="D8" s="106" t="n">
         <v>11.522</v>
       </c>
-      <c r="E8" s="108" t="n">
+      <c r="E8" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="108" t="n">
+      <c r="F8" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G8" s="108" t="n">
+      <c r="G8" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H8" s="109" t="n">
+      <c r="H8" s="111" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I8" s="109" t="n">
+      <c r="I8" s="111" t="n">
         <v>0.92</v>
       </c>
-      <c r="J8" s="108" t="n">
+      <c r="J8" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K8" s="109" t="n">
+      <c r="K8" s="111" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -13142,38 +13307,38 @@
           <t>Kiran Trading Company_Ship to</t>
         </is>
       </c>
-      <c r="B9" s="94" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="C9" s="94" t="inlineStr">
+      <c r="C9" s="96" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="D9" s="104" t="n">
+      <c r="D9" s="106" t="n">
         <v>10.078</v>
       </c>
-      <c r="E9" s="108" t="n">
+      <c r="E9" s="110" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="108" t="n">
+      <c r="F9" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="108" t="n">
+      <c r="G9" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="109" t="n">
+      <c r="H9" s="111" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I9" s="109" t="n">
+      <c r="I9" s="111" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J9" s="108" t="n">
+      <c r="J9" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K9" s="109" t="n">
+      <c r="K9" s="111" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -13183,38 +13348,38 @@
           <t>Avenue Supermarts Ltd.-DC-1049</t>
         </is>
       </c>
-      <c r="B10" s="94" t="inlineStr">
+      <c r="B10" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D10" s="104" t="n">
+      <c r="D10" s="106" t="n">
         <v>8.492000000000001</v>
       </c>
-      <c r="E10" s="108" t="n">
+      <c r="E10" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F10" s="108" t="n">
+      <c r="F10" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G10" s="108" t="n">
+      <c r="G10" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H10" s="109" t="n">
+      <c r="H10" s="111" t="n">
         <v>0.93</v>
       </c>
-      <c r="I10" s="109" t="n">
+      <c r="I10" s="111" t="n">
         <v>0.86</v>
       </c>
-      <c r="J10" s="108" t="n">
+      <c r="J10" s="110" t="n">
         <v>60</v>
       </c>
-      <c r="K10" s="109" t="n">
+      <c r="K10" s="111" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -13224,38 +13389,38 @@
           <t>Wellness Forever Medicare Ltd</t>
         </is>
       </c>
-      <c r="B11" s="94" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="C11" s="94" t="inlineStr">
+      <c r="C11" s="96" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="D11" s="104" t="n">
+      <c r="D11" s="106" t="n">
         <v>8.262</v>
       </c>
-      <c r="E11" s="108" t="n">
+      <c r="E11" s="110" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="108" t="n">
+      <c r="F11" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G11" s="108" t="n">
+      <c r="G11" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H11" s="109" t="n">
+      <c r="H11" s="111" t="n">
         <v>0.97</v>
       </c>
-      <c r="I11" s="109" t="n">
+      <c r="I11" s="111" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J11" s="108" t="n">
+      <c r="J11" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K11" s="109" t="n">
+      <c r="K11" s="111" t="n">
         <v>0.11</v>
       </c>
     </row>
@@ -13265,38 +13430,38 @@
           <t>Apollo Healthco Limited_Faridabad</t>
         </is>
       </c>
-      <c r="B12" s="94" t="inlineStr">
+      <c r="B12" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D12" s="104" t="n">
+      <c r="D12" s="106" t="n">
         <v>7.068</v>
       </c>
-      <c r="E12" s="108" t="n">
+      <c r="E12" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="108" t="n">
+      <c r="F12" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G12" s="108" t="n">
+      <c r="G12" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H12" s="109" t="n">
+      <c r="H12" s="111" t="n">
         <v>0.91</v>
       </c>
-      <c r="I12" s="109" t="n">
+      <c r="I12" s="111" t="n">
         <v>0.98</v>
       </c>
-      <c r="J12" s="108" t="n">
+      <c r="J12" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K12" s="109" t="n">
+      <c r="K12" s="111" t="n">
         <v>0.11</v>
       </c>
     </row>
@@ -13306,38 +13471,38 @@
           <t>Avenue Supermarts Ltd.-DC-1050</t>
         </is>
       </c>
-      <c r="B13" s="94" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C13" s="94" t="inlineStr">
+      <c r="C13" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D13" s="104" t="n">
+      <c r="D13" s="106" t="n">
         <v>6.609</v>
       </c>
-      <c r="E13" s="108" t="n">
+      <c r="E13" s="110" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="108" t="n">
+      <c r="F13" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G13" s="108" t="n">
+      <c r="G13" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H13" s="109" t="n">
+      <c r="H13" s="111" t="n">
         <v>0.98</v>
       </c>
-      <c r="I13" s="109" t="n">
+      <c r="I13" s="111" t="n">
         <v>0.88</v>
       </c>
-      <c r="J13" s="108" t="n">
+      <c r="J13" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K13" s="109" t="n">
+      <c r="K13" s="111" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -13347,38 +13512,38 @@
           <t>Avenue Supermarts Ltd.-DC-1068</t>
         </is>
       </c>
-      <c r="B14" s="94" t="inlineStr">
+      <c r="B14" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D14" s="104" t="n">
+      <c r="D14" s="106" t="n">
         <v>5.917</v>
       </c>
-      <c r="E14" s="108" t="n">
+      <c r="E14" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F14" s="108" t="n">
+      <c r="F14" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="108" t="n">
+      <c r="G14" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H14" s="109" t="n">
+      <c r="H14" s="111" t="n">
         <v>0.92</v>
       </c>
-      <c r="I14" s="109" t="n">
+      <c r="I14" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="J14" s="108" t="n">
+      <c r="J14" s="110" t="n">
         <v>60</v>
       </c>
-      <c r="K14" s="109" t="n">
+      <c r="K14" s="111" t="n">
         <v>-0.12</v>
       </c>
     </row>
@@ -13388,38 +13553,38 @@
           <t>Az Enterprises(Apollo/More)Mt</t>
         </is>
       </c>
-      <c r="B15" s="94" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
+      <c r="C15" s="96" t="inlineStr">
         <is>
           <t>South-1</t>
         </is>
       </c>
-      <c r="D15" s="104" t="n">
+      <c r="D15" s="106" t="n">
         <v>5.536</v>
       </c>
-      <c r="E15" s="108" t="n">
+      <c r="E15" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="108" t="n">
+      <c r="F15" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="108" t="n">
+      <c r="G15" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H15" s="109" t="n">
+      <c r="H15" s="111" t="n">
         <v>0.96</v>
       </c>
-      <c r="I15" s="109" t="n">
+      <c r="I15" s="111" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J15" s="108" t="n">
+      <c r="J15" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K15" s="109" t="n">
+      <c r="K15" s="111" t="n">
         <v>0.17</v>
       </c>
     </row>
@@ -13429,38 +13594,38 @@
           <t>D.L. Sales - MT</t>
         </is>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B16" s="96" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="96" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="D16" s="104" t="n">
+      <c r="D16" s="106" t="n">
         <v>5.191</v>
       </c>
-      <c r="E16" s="108" t="n">
+      <c r="E16" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F16" s="108" t="n">
+      <c r="F16" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="108" t="n">
+      <c r="G16" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H16" s="109" t="n">
+      <c r="H16" s="111" t="n">
         <v>0.92</v>
       </c>
-      <c r="I16" s="109" t="n">
+      <c r="I16" s="111" t="n">
         <v>0.92</v>
       </c>
-      <c r="J16" s="108" t="n">
+      <c r="J16" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K16" s="109" t="n">
+      <c r="K16" s="111" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -13470,38 +13635,38 @@
           <t>Sancus Networks Private Limited-RMT</t>
         </is>
       </c>
-      <c r="B17" s="94" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C17" s="94" t="inlineStr">
+      <c r="C17" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D17" s="104" t="n">
+      <c r="D17" s="106" t="n">
         <v>5.053</v>
       </c>
-      <c r="E17" s="108" t="n">
+      <c r="E17" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F17" s="108" t="n">
+      <c r="F17" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G17" s="108" t="n">
+      <c r="G17" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H17" s="109" t="n">
+      <c r="H17" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="I17" s="109" t="n">
+      <c r="I17" s="111" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J17" s="108" t="n">
+      <c r="J17" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K17" s="109" t="n">
+      <c r="K17" s="111" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -13511,38 +13676,38 @@
           <t>Az Enterprises</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
+      <c r="B18" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="96" t="inlineStr">
         <is>
           <t>South-1</t>
         </is>
       </c>
-      <c r="D18" s="104" t="n">
+      <c r="D18" s="106" t="n">
         <v>4.457</v>
       </c>
-      <c r="E18" s="108" t="n">
+      <c r="E18" s="110" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="108" t="n">
+      <c r="F18" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G18" s="108" t="n">
+      <c r="G18" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H18" s="109" t="n">
+      <c r="H18" s="111" t="n">
         <v>0.98</v>
       </c>
-      <c r="I18" s="109" t="n">
+      <c r="I18" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="J18" s="108" t="n">
+      <c r="J18" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="K18" s="109" t="n">
+      <c r="K18" s="111" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -13552,38 +13717,38 @@
           <t>Vanaja Agencies_Mt</t>
         </is>
       </c>
-      <c r="B19" s="94" t="inlineStr">
+      <c r="B19" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C19" s="94" t="inlineStr">
+      <c r="C19" s="96" t="inlineStr">
         <is>
           <t>South-2</t>
         </is>
       </c>
-      <c r="D19" s="104" t="n">
+      <c r="D19" s="106" t="n">
         <v>4.429</v>
       </c>
-      <c r="E19" s="108" t="n">
+      <c r="E19" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F19" s="108" t="n">
+      <c r="F19" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G19" s="108" t="n">
+      <c r="G19" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H19" s="109" t="n">
+      <c r="H19" s="111" t="n">
         <v>0.98</v>
       </c>
-      <c r="I19" s="109" t="n">
+      <c r="I19" s="111" t="n">
         <v>0.85</v>
       </c>
-      <c r="J19" s="108" t="n">
+      <c r="J19" s="110" t="n">
         <v>60</v>
       </c>
-      <c r="K19" s="109" t="n">
+      <c r="K19" s="111" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -13593,38 +13758,38 @@
           <t>BALAJI ASSOCIATES Distributor MT</t>
         </is>
       </c>
-      <c r="B20" s="94" t="inlineStr">
+      <c r="B20" s="96" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="96" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="D20" s="104" t="n">
+      <c r="D20" s="106" t="n">
         <v>4.257</v>
       </c>
-      <c r="E20" s="108" t="n">
+      <c r="E20" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F20" s="108" t="n">
+      <c r="F20" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G20" s="108" t="n">
+      <c r="G20" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H20" s="109" t="n">
+      <c r="H20" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="I20" s="109" t="n">
+      <c r="I20" s="111" t="n">
         <v>0.83</v>
       </c>
-      <c r="J20" s="108" t="n">
+      <c r="J20" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="K20" s="109" t="n">
+      <c r="K20" s="111" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -13634,38 +13799,38 @@
           <t>Vanaja Agencies MT_Dmart</t>
         </is>
       </c>
-      <c r="B21" s="94" t="inlineStr">
+      <c r="B21" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C21" s="94" t="inlineStr">
+      <c r="C21" s="96" t="inlineStr">
         <is>
           <t>South-2</t>
         </is>
       </c>
-      <c r="D21" s="104" t="n">
+      <c r="D21" s="106" t="n">
         <v>4.215</v>
       </c>
-      <c r="E21" s="108" t="n">
+      <c r="E21" s="110" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="108" t="n">
+      <c r="F21" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="108" t="n">
+      <c r="G21" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H21" s="109" t="n">
+      <c r="H21" s="111" t="n">
         <v>0.88</v>
       </c>
-      <c r="I21" s="109" t="n">
+      <c r="I21" s="111" t="n">
         <v>0.88</v>
       </c>
-      <c r="J21" s="108" t="n">
+      <c r="J21" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K21" s="109" t="n">
+      <c r="K21" s="111" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -13675,38 +13840,38 @@
           <t>Avenue Supermarts Ltd.-DC-1054</t>
         </is>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B22" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="96" t="inlineStr">
         <is>
           <t>South-2</t>
         </is>
       </c>
-      <c r="D22" s="104" t="n">
+      <c r="D22" s="106" t="n">
         <v>4.151</v>
       </c>
-      <c r="E22" s="108" t="n">
+      <c r="E22" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="108" t="n">
+      <c r="F22" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G22" s="108" t="n">
+      <c r="G22" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H22" s="109" t="n">
+      <c r="H22" s="111" t="n">
         <v>0.97</v>
       </c>
-      <c r="I22" s="109" t="n">
+      <c r="I22" s="111" t="n">
         <v>0.97</v>
       </c>
-      <c r="J22" s="108" t="n">
+      <c r="J22" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K22" s="109" t="n">
+      <c r="K22" s="111" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -13716,38 +13881,38 @@
           <t>M/S KOTTARAM BUSINESS CORPORATION-MT</t>
         </is>
       </c>
-      <c r="B23" s="94" t="inlineStr">
+      <c r="B23" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C23" s="94" t="inlineStr">
+      <c r="C23" s="96" t="inlineStr">
         <is>
           <t>South-1</t>
         </is>
       </c>
-      <c r="D23" s="104" t="n">
+      <c r="D23" s="106" t="n">
         <v>4.039</v>
       </c>
-      <c r="E23" s="108" t="n">
+      <c r="E23" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="108" t="n">
+      <c r="F23" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G23" s="108" t="n">
+      <c r="G23" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H23" s="109" t="n">
+      <c r="H23" s="111" t="n">
         <v>0.92</v>
       </c>
-      <c r="I23" s="109" t="n">
+      <c r="I23" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="J23" s="108" t="n">
+      <c r="J23" s="110" t="n">
         <v>60</v>
       </c>
-      <c r="K23" s="109" t="n">
+      <c r="K23" s="111" t="n">
         <v>-0.12</v>
       </c>
     </row>
@@ -13757,38 +13922,38 @@
           <t>Apollo Healthco Limited-Hubbli</t>
         </is>
       </c>
-      <c r="B24" s="94" t="inlineStr">
+      <c r="B24" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C24" s="96" t="inlineStr">
         <is>
           <t>South-1</t>
         </is>
       </c>
-      <c r="D24" s="104" t="n">
+      <c r="D24" s="106" t="n">
         <v>4.027</v>
       </c>
-      <c r="E24" s="108" t="n">
+      <c r="E24" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="108" t="n">
+      <c r="F24" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G24" s="108" t="n">
+      <c r="G24" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H24" s="109" t="n">
+      <c r="H24" s="111" t="n">
         <v>0.9</v>
       </c>
-      <c r="I24" s="109" t="n">
+      <c r="I24" s="111" t="n">
         <v>0.86</v>
       </c>
-      <c r="J24" s="108" t="n">
+      <c r="J24" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K24" s="109" t="n">
+      <c r="K24" s="111" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -13798,38 +13963,38 @@
           <t>Apollo Healthco Limited-Bangalore</t>
         </is>
       </c>
-      <c r="B25" s="94" t="inlineStr">
+      <c r="B25" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C25" s="94" t="inlineStr">
+      <c r="C25" s="96" t="inlineStr">
         <is>
           <t>South-1</t>
         </is>
       </c>
-      <c r="D25" s="104" t="n">
+      <c r="D25" s="106" t="n">
         <v>3.987</v>
       </c>
-      <c r="E25" s="108" t="n">
+      <c r="E25" s="110" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="108" t="n">
+      <c r="F25" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G25" s="108" t="n">
+      <c r="G25" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H25" s="109" t="n">
+      <c r="H25" s="111" t="n">
         <v>0.98</v>
       </c>
-      <c r="I25" s="109" t="n">
+      <c r="I25" s="111" t="n">
         <v>0.91</v>
       </c>
-      <c r="J25" s="108" t="n">
+      <c r="J25" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K25" s="109" t="n">
+      <c r="K25" s="111" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -13839,38 +14004,38 @@
           <t>Avenue Supermarts Ltd.-DC-1091</t>
         </is>
       </c>
-      <c r="B26" s="94" t="inlineStr">
+      <c r="B26" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="C26" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D26" s="104" t="n">
+      <c r="D26" s="106" t="n">
         <v>3.818</v>
       </c>
-      <c r="E26" s="108" t="n">
+      <c r="E26" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F26" s="108" t="n">
+      <c r="F26" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G26" s="108" t="n">
+      <c r="G26" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H26" s="109" t="n">
+      <c r="H26" s="111" t="n">
         <v>0.91</v>
       </c>
-      <c r="I26" s="109" t="n">
+      <c r="I26" s="111" t="n">
         <v>0.86</v>
       </c>
-      <c r="J26" s="108" t="n">
+      <c r="J26" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K26" s="109" t="n">
+      <c r="K26" s="111" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -13880,38 +14045,38 @@
           <t>VENKATESHWARA AGENCIES-TG</t>
         </is>
       </c>
-      <c r="B27" s="94" t="inlineStr">
+      <c r="B27" s="96" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="C27" s="94" t="inlineStr">
+      <c r="C27" s="96" t="inlineStr">
         <is>
           <t>South-2</t>
         </is>
       </c>
-      <c r="D27" s="104" t="n">
+      <c r="D27" s="106" t="n">
         <v>3.791</v>
       </c>
-      <c r="E27" s="108" t="n">
+      <c r="E27" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="108" t="n">
+      <c r="F27" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="108" t="n">
+      <c r="G27" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H27" s="109" t="n">
+      <c r="H27" s="111" t="n">
         <v>0.93</v>
       </c>
-      <c r="I27" s="109" t="n">
+      <c r="I27" s="111" t="n">
         <v>0.86</v>
       </c>
-      <c r="J27" s="108" t="n">
+      <c r="J27" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="K27" s="109" t="n">
+      <c r="K27" s="111" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -13921,38 +14086,38 @@
           <t>APOLLO HEALTHCO LIMITED-WB-2</t>
         </is>
       </c>
-      <c r="B28" s="94" t="inlineStr">
+      <c r="B28" s="96" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="C28" s="94" t="inlineStr">
+      <c r="C28" s="96" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="D28" s="104" t="n">
+      <c r="D28" s="106" t="n">
         <v>3.592</v>
       </c>
-      <c r="E28" s="108" t="n">
+      <c r="E28" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F28" s="108" t="n">
+      <c r="F28" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G28" s="108" t="n">
+      <c r="G28" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H28" s="109" t="n">
+      <c r="H28" s="111" t="n">
         <v>0.93</v>
       </c>
-      <c r="I28" s="109" t="n">
+      <c r="I28" s="111" t="n">
         <v>0.92</v>
       </c>
-      <c r="J28" s="108" t="n">
+      <c r="J28" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K28" s="109" t="n">
+      <c r="K28" s="111" t="n">
         <v>-0.05</v>
       </c>
     </row>
@@ -13962,38 +14127,38 @@
           <t>Reliance Retail Limited_Fr87</t>
         </is>
       </c>
-      <c r="B29" s="94" t="inlineStr">
+      <c r="B29" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C29" s="94" t="inlineStr">
+      <c r="C29" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D29" s="104" t="n">
+      <c r="D29" s="106" t="n">
         <v>3.479</v>
       </c>
-      <c r="E29" s="108" t="n">
+      <c r="E29" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F29" s="108" t="n">
+      <c r="F29" s="110" t="n">
         <v>21</v>
       </c>
-      <c r="G29" s="108" t="n">
+      <c r="G29" s="110" t="n">
         <v>200</v>
       </c>
-      <c r="H29" s="109" t="n">
+      <c r="H29" s="111" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I29" s="109" t="n">
+      <c r="I29" s="111" t="n">
         <v>0.8</v>
       </c>
-      <c r="J29" s="108" t="n">
+      <c r="J29" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K29" s="109" t="n">
+      <c r="K29" s="111" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -14003,38 +14168,38 @@
           <t>Reliance Retail Limited_SL6S</t>
         </is>
       </c>
-      <c r="B30" s="94" t="inlineStr">
+      <c r="B30" s="96" t="inlineStr">
         <is>
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C30" s="96" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="D30" s="104" t="n">
+      <c r="D30" s="106" t="n">
         <v>3.425</v>
       </c>
-      <c r="E30" s="108" t="n">
+      <c r="E30" s="110" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="108" t="n">
+      <c r="F30" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G30" s="108" t="n">
+      <c r="G30" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H30" s="109" t="n">
+      <c r="H30" s="111" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I30" s="109" t="n">
+      <c r="I30" s="111" t="n">
         <v>0.96</v>
       </c>
-      <c r="J30" s="108" t="n">
+      <c r="J30" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K30" s="109" t="n">
+      <c r="K30" s="111" t="n">
         <v>0.24</v>
       </c>
     </row>
@@ -14044,38 +14209,38 @@
           <t>Reliance Retail Limited Ce08</t>
         </is>
       </c>
-      <c r="B31" s="94" t="inlineStr">
+      <c r="B31" s="96" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="C31" s="94" t="inlineStr">
+      <c r="C31" s="96" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="D31" s="104" t="n">
+      <c r="D31" s="106" t="n">
         <v>3.419</v>
       </c>
-      <c r="E31" s="108" t="n">
+      <c r="E31" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F31" s="108" t="n">
+      <c r="F31" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G31" s="108" t="n">
+      <c r="G31" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H31" s="109" t="n">
+      <c r="H31" s="111" t="n">
         <v>0.95</v>
       </c>
-      <c r="I31" s="109" t="n">
+      <c r="I31" s="111" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="J31" s="108" t="n">
+      <c r="J31" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="K31" s="109" t="n">
+      <c r="K31" s="111" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -14085,38 +14250,38 @@
           <t>Kiran Trading Co_Shipto (Solapur)</t>
         </is>
       </c>
-      <c r="B32" s="94" t="inlineStr">
+      <c r="B32" s="96" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="C32" s="94" t="inlineStr">
+      <c r="C32" s="96" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="D32" s="104" t="n">
+      <c r="D32" s="106" t="n">
         <v>3.326</v>
       </c>
-      <c r="E32" s="108" t="n">
+      <c r="E32" s="110" t="n">
         <v>10</v>
       </c>
-      <c r="F32" s="108" t="n">
+      <c r="F32" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="G32" s="108" t="n">
+      <c r="G32" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="H32" s="109" t="n">
+      <c r="H32" s="111" t="n">
         <v>0.9</v>
       </c>
-      <c r="I32" s="109" t="n">
+      <c r="I32" s="111" t="n">
         <v>0.89</v>
       </c>
-      <c r="J32" s="108" t="n">
+      <c r="J32" s="110" t="n">
         <v>20</v>
       </c>
-      <c r="K32" s="109" t="n">
+      <c r="K32" s="111" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -14126,38 +14291,38 @@
           <t>RELIANCE RETAIL LIMITED-SF92</t>
         </is>
       </c>
-      <c r="B33" s="94" t="inlineStr">
+      <c r="B33" s="96" t="inlineStr">
         <is>
           <t>Kolkata</t>
         </is>
       </c>
-      <c r="C33" s="94" t="inlineStr">
+      <c r="C33" s="96" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="D33" s="104" t="n">
+      <c r="D33" s="106" t="n">
         <v>3.107</v>
       </c>
-      <c r="E33" s="108" t="n">
+      <c r="E33" s="110" t="n">
         <v>7</v>
       </c>
-      <c r="F33" s="108" t="n">
+      <c r="F33" s="110" t="n">
         <v>30</v>
       </c>
-      <c r="G33" s="108" t="n">
+      <c r="G33" s="110" t="n">
         <v>100</v>
       </c>
-      <c r="H33" s="109" t="n">
+      <c r="H33" s="111" t="n">
         <v>0.9</v>
       </c>
-      <c r="I33" s="109" t="n">
+      <c r="I33" s="111" t="n">
         <v>0.91</v>
       </c>
-      <c r="J33" s="108" t="n">
+      <c r="J33" s="110" t="n">
         <v>45</v>
       </c>
-      <c r="K33" s="109" t="n">
+      <c r="K33" s="111" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -14262,31 +14427,31 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C4" s="110" t="inlineStr">
+      <c r="C4" s="112" t="inlineStr">
         <is>
           <t>Rice Serum 30ml (new)</t>
         </is>
       </c>
-      <c r="D4" s="108" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>Jul'26</t>
         </is>
       </c>
-      <c r="E4" s="108" t="n">
+      <c r="E4" s="110" t="n">
         <v>40000</v>
       </c>
-      <c r="F4" s="108" t="n">
+      <c r="F4" s="110" t="n">
         <v>1200</v>
       </c>
-      <c r="G4" s="108" t="inlineStr">
+      <c r="G4" s="110" t="inlineStr">
         <is>
           <t>Fast</t>
         </is>
       </c>
-      <c r="H4" s="109" t="n">
+      <c r="H4" s="111" t="n">
         <v>0.1</v>
       </c>
-      <c r="I4" s="111" t="n">
+      <c r="I4" s="113" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -14301,31 +14466,31 @@
           <t>Sun Care</t>
         </is>
       </c>
-      <c r="C5" s="110" t="inlineStr">
+      <c r="C5" s="112" t="inlineStr">
         <is>
           <t>SPF60 Gel 100g (new)</t>
         </is>
       </c>
-      <c r="D5" s="108" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
         <is>
           <t>Jun'26</t>
         </is>
       </c>
-      <c r="E5" s="108" t="n">
+      <c r="E5" s="110" t="n">
         <v>30000</v>
       </c>
-      <c r="F5" s="108" t="n">
+      <c r="F5" s="110" t="n">
         <v>900</v>
       </c>
-      <c r="G5" s="108" t="inlineStr">
+      <c r="G5" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" s="109" t="n">
+      <c r="H5" s="111" t="n">
         <v>0.08</v>
       </c>
-      <c r="I5" s="111" t="n">
+      <c r="I5" s="113" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -14340,31 +14505,31 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C6" s="110" t="inlineStr">
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>Radiance Toner (new)</t>
         </is>
       </c>
-      <c r="D6" s="108" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>Aug'26</t>
         </is>
       </c>
-      <c r="E6" s="108" t="n">
+      <c r="E6" s="110" t="n">
         <v>25000</v>
       </c>
-      <c r="F6" s="108" t="n">
+      <c r="F6" s="110" t="n">
         <v>700</v>
       </c>
-      <c r="G6" s="108" t="inlineStr">
+      <c r="G6" s="110" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" s="109" t="n">
+      <c r="H6" s="111" t="n">
         <v>0.12</v>
       </c>
-      <c r="I6" s="111" t="n">
+      <c r="I6" s="113" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -14507,28 +14672,28 @@
           <t>Sun Care</t>
         </is>
       </c>
-      <c r="C4" s="108" t="inlineStr">
+      <c r="C4" s="110" t="inlineStr">
         <is>
           <t>Jun'26</t>
         </is>
       </c>
-      <c r="D4" s="110" t="inlineStr">
+      <c r="D4" s="112" t="inlineStr">
         <is>
           <t>Endcap + Price Off</t>
         </is>
       </c>
-      <c r="E4" s="110" t="inlineStr">
+      <c r="E4" s="112" t="inlineStr">
         <is>
           <t>D-Mart</t>
         </is>
       </c>
-      <c r="F4" s="109" t="n">
+      <c r="F4" s="111" t="n">
         <v>0.15</v>
       </c>
-      <c r="G4" s="109" t="n">
+      <c r="G4" s="111" t="n">
         <v>0.2</v>
       </c>
-      <c r="H4" s="110" t="inlineStr">
+      <c r="H4" s="112" t="inlineStr">
         <is>
           <t>Summer sun push</t>
         </is>
@@ -14545,28 +14710,28 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C5" s="108" t="inlineStr">
+      <c r="C5" s="110" t="inlineStr">
         <is>
           <t>Jul'26</t>
         </is>
       </c>
-      <c r="D5" s="110" t="inlineStr">
+      <c r="D5" s="112" t="inlineStr">
         <is>
           <t>BOGO</t>
         </is>
       </c>
-      <c r="E5" s="110" t="inlineStr">
+      <c r="E5" s="112" t="inlineStr">
         <is>
           <t>Reliance Retail</t>
         </is>
       </c>
-      <c r="F5" s="109" t="n">
+      <c r="F5" s="111" t="n">
         <v>0.2</v>
       </c>
-      <c r="G5" s="109" t="n">
+      <c r="G5" s="111" t="n">
         <v>0.15</v>
       </c>
-      <c r="H5" s="110" t="inlineStr">
+      <c r="H5" s="112" t="inlineStr">
         <is>
           <t>Monsoon face care</t>
         </is>
@@ -14583,28 +14748,28 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C6" s="108" t="inlineStr">
+      <c r="C6" s="110" t="inlineStr">
         <is>
           <t>Jun'26</t>
         </is>
       </c>
-      <c r="D6" s="110" t="inlineStr">
+      <c r="D6" s="112" t="inlineStr">
         <is>
           <t>Gondola + Visibility</t>
         </is>
       </c>
-      <c r="E6" s="110" t="inlineStr">
+      <c r="E6" s="112" t="inlineStr">
         <is>
           <t>Health &amp; Glow</t>
         </is>
       </c>
-      <c r="F6" s="109" t="n">
+      <c r="F6" s="111" t="n">
         <v>0.1</v>
       </c>
-      <c r="G6" s="109" t="n">
+      <c r="G6" s="111" t="n">
         <v>0.12</v>
       </c>
-      <c r="H6" s="110" t="inlineStr">
+      <c r="H6" s="112" t="inlineStr">
         <is>
           <t>Derma focus</t>
         </is>
@@ -14621,28 +14786,28 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="C7" s="108" t="inlineStr">
+      <c r="C7" s="110" t="inlineStr">
         <is>
           <t>Aug'26</t>
         </is>
       </c>
-      <c r="D7" s="110" t="inlineStr">
+      <c r="D7" s="112" t="inlineStr">
         <is>
           <t>Digital Campaign + SIS</t>
         </is>
       </c>
-      <c r="E7" s="110" t="inlineStr">
+      <c r="E7" s="112" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="F7" s="109" t="n">
+      <c r="F7" s="111" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" s="109" t="n">
+      <c r="G7" s="111" t="n">
         <v>0.18</v>
       </c>
-      <c r="H7" s="110" t="inlineStr">
+      <c r="H7" s="112" t="inlineStr">
         <is>
           <t>Gen-Z push</t>
         </is>
@@ -14659,28 +14824,28 @@
           <t>Baby</t>
         </is>
       </c>
-      <c r="C8" s="108" t="inlineStr">
+      <c r="C8" s="110" t="inlineStr">
         <is>
           <t>Jul'26</t>
         </is>
       </c>
-      <c r="D8" s="110" t="inlineStr">
+      <c r="D8" s="112" t="inlineStr">
         <is>
           <t>Retail Festival</t>
         </is>
       </c>
-      <c r="E8" s="110" t="inlineStr">
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F8" s="109" t="n">
+      <c r="F8" s="111" t="n">
         <v>0.12</v>
       </c>
-      <c r="G8" s="109" t="n">
+      <c r="G8" s="111" t="n">
         <v>0.1</v>
       </c>
-      <c r="H8" s="110" t="inlineStr">
+      <c r="H8" s="112" t="inlineStr">
         <is>
           <t>Baby fest</t>
         </is>
@@ -14857,43 +15022,43 @@
           <t>Face</t>
         </is>
       </c>
-      <c r="B4" s="90" t="n">
+      <c r="B4" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="90" t="n">
+      <c r="C4" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="90" t="n">
+      <c r="D4" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="90" t="n">
+      <c r="E4" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="90" t="n">
+      <c r="F4" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="G4" s="90" t="n">
+      <c r="G4" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="H4" s="90" t="n">
+      <c r="H4" s="92" t="n">
         <v>1.15</v>
       </c>
-      <c r="I4" s="90" t="n">
+      <c r="I4" s="92" t="n">
         <v>1.2</v>
       </c>
-      <c r="J4" s="90" t="n">
+      <c r="J4" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="K4" s="90" t="n">
+      <c r="K4" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="L4" s="90" t="n">
+      <c r="L4" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="M4" s="90" t="n">
+      <c r="M4" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="N4" s="112">
+      <c r="N4" s="114">
         <f>AVERAGE(B4:M4)</f>
         <v/>
       </c>
@@ -14904,43 +15069,43 @@
           <t>Hair</t>
         </is>
       </c>
-      <c r="B5" s="90" t="n">
+      <c r="B5" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="C5" s="90" t="n">
+      <c r="C5" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="90" t="n">
+      <c r="D5" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="90" t="n">
+      <c r="E5" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="90" t="n">
+      <c r="F5" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="G5" s="90" t="n">
+      <c r="G5" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="H5" s="90" t="n">
+      <c r="H5" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="I5" s="90" t="n">
+      <c r="I5" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="J5" s="90" t="n">
+      <c r="J5" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="90" t="n">
+      <c r="K5" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="90" t="n">
+      <c r="L5" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="M5" s="90" t="n">
+      <c r="M5" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="N5" s="112">
+      <c r="N5" s="114">
         <f>AVERAGE(B5:M5)</f>
         <v/>
       </c>
@@ -14951,43 +15116,43 @@
           <t>Body</t>
         </is>
       </c>
-      <c r="B6" s="90" t="n">
+      <c r="B6" s="92" t="n">
         <v>0.75</v>
       </c>
-      <c r="C6" s="90" t="n">
+      <c r="C6" s="92" t="n">
         <v>0.7</v>
       </c>
-      <c r="D6" s="90" t="n">
+      <c r="D6" s="92" t="n">
         <v>0.7</v>
       </c>
-      <c r="E6" s="90" t="n">
+      <c r="E6" s="92" t="n">
         <v>0.75</v>
       </c>
-      <c r="F6" s="90" t="n">
+      <c r="F6" s="92" t="n">
         <v>0.85</v>
       </c>
-      <c r="G6" s="90" t="n">
+      <c r="G6" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="H6" s="90" t="n">
+      <c r="H6" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="I6" s="90" t="n">
+      <c r="I6" s="92" t="n">
         <v>1.25</v>
       </c>
-      <c r="J6" s="90" t="n">
+      <c r="J6" s="92" t="n">
         <v>1.45</v>
       </c>
-      <c r="K6" s="90" t="n">
+      <c r="K6" s="92" t="n">
         <v>1.5</v>
       </c>
-      <c r="L6" s="90" t="n">
+      <c r="L6" s="92" t="n">
         <v>1.4</v>
       </c>
-      <c r="M6" s="90" t="n">
+      <c r="M6" s="92" t="n">
         <v>1.2</v>
       </c>
-      <c r="N6" s="112">
+      <c r="N6" s="114">
         <f>AVERAGE(B6:M6)</f>
         <v/>
       </c>
@@ -14998,43 +15163,43 @@
           <t>Baby</t>
         </is>
       </c>
-      <c r="B7" s="90" t="n">
+      <c r="B7" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="90" t="n">
+      <c r="C7" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="90" t="n">
+      <c r="D7" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="90" t="n">
+      <c r="E7" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="90" t="n">
+      <c r="F7" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="90" t="n">
+      <c r="G7" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="H7" s="90" t="n">
+      <c r="H7" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="I7" s="90" t="n">
+      <c r="I7" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="J7" s="90" t="n">
+      <c r="J7" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="K7" s="90" t="n">
+      <c r="K7" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="L7" s="90" t="n">
+      <c r="L7" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="90" t="n">
+      <c r="M7" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="112">
+      <c r="N7" s="114">
         <f>AVERAGE(B7:M7)</f>
         <v/>
       </c>
@@ -15045,43 +15210,43 @@
           <t>Hair Care</t>
         </is>
       </c>
-      <c r="B8" s="90" t="n">
+      <c r="B8" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="C8" s="90" t="n">
+      <c r="C8" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="90" t="n">
+      <c r="D8" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="90" t="n">
+      <c r="E8" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="90" t="n">
+      <c r="F8" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="G8" s="90" t="n">
+      <c r="G8" s="92" t="n">
         <v>1.1</v>
       </c>
-      <c r="H8" s="90" t="n">
+      <c r="H8" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="I8" s="90" t="n">
+      <c r="I8" s="92" t="n">
         <v>1.05</v>
       </c>
-      <c r="J8" s="90" t="n">
+      <c r="J8" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="90" t="n">
+      <c r="K8" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="90" t="n">
+      <c r="L8" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="M8" s="90" t="n">
+      <c r="M8" s="92" t="n">
         <v>0.95</v>
       </c>
-      <c r="N8" s="112">
+      <c r="N8" s="114">
         <f>AVERAGE(B8:M8)</f>
         <v/>
       </c>
@@ -15092,43 +15257,43 @@
           <t>Fragrances</t>
         </is>
       </c>
-      <c r="B9" s="90" t="n">
+      <c r="B9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="90" t="n">
+      <c r="C9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="90" t="n">
+      <c r="D9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="90" t="n">
+      <c r="E9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="90" t="n">
+      <c r="F9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="90" t="n">
+      <c r="G9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="90" t="n">
+      <c r="H9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="90" t="n">
+      <c r="I9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="90" t="n">
+      <c r="J9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="90" t="n">
+      <c r="K9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="90" t="n">
+      <c r="L9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="90" t="n">
+      <c r="M9" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="112">
+      <c r="N9" s="114">
         <f>AVERAGE(B9:M9)</f>
         <v/>
       </c>
@@ -15139,90 +15304,90 @@
           <t>Styling Products</t>
         </is>
       </c>
-      <c r="B10" s="90" t="n">
+      <c r="B10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="90" t="n">
+      <c r="C10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="90" t="n">
+      <c r="D10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="90" t="n">
+      <c r="E10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="90" t="n">
+      <c r="F10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="90" t="n">
+      <c r="G10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="90" t="n">
+      <c r="H10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="90" t="n">
+      <c r="I10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="90" t="n">
+      <c r="J10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="90" t="n">
+      <c r="K10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="90" t="n">
+      <c r="L10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="M10" s="90" t="n">
+      <c r="M10" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="114">
         <f>AVERAGE(B10:M10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="113" t="inlineStr">
+      <c r="A11" s="115" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="B11" s="90" t="n">
+      <c r="B11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="90" t="n">
+      <c r="C11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="90" t="n">
+      <c r="D11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="90" t="n">
+      <c r="E11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="90" t="n">
+      <c r="F11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="90" t="n">
+      <c r="G11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="90" t="n">
+      <c r="H11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="90" t="n">
+      <c r="I11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="90" t="n">
+      <c r="J11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="90" t="n">
+      <c r="K11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="90" t="n">
+      <c r="L11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="90" t="n">
+      <c r="M11" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="N11" s="114">
+      <c r="N11" s="116">
         <f>AVERAGE(B11:M11)</f>
         <v/>
       </c>
@@ -15281,650 +15446,650 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="94" t="n">
+      <c r="A3" s="96" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="94" t="inlineStr">
+      <c r="B3" s="96" t="inlineStr">
         <is>
           <t>Apr'25</t>
         </is>
       </c>
-      <c r="C3" s="94" t="inlineStr">
+      <c r="C3" s="96" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="94" t="n">
+      <c r="A4" s="96" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="94" t="inlineStr">
+      <c r="B4" s="96" t="inlineStr">
         <is>
           <t>May'25</t>
         </is>
       </c>
-      <c r="C4" s="94" t="inlineStr">
+      <c r="C4" s="96" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="94" t="n">
+      <c r="A5" s="96" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="94" t="inlineStr">
+      <c r="B5" s="96" t="inlineStr">
         <is>
           <t>Jun'25</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
+      <c r="C5" s="96" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="D5" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="n">
+      <c r="A6" s="96" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="94" t="inlineStr">
+      <c r="B6" s="96" t="inlineStr">
         <is>
           <t>Jul'25</t>
         </is>
       </c>
-      <c r="C6" s="94" t="inlineStr">
+      <c r="C6" s="96" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="D6" s="94" t="n">
+      <c r="D6" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="94" t="n">
+      <c r="A7" s="96" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="94" t="inlineStr">
+      <c r="B7" s="96" t="inlineStr">
         <is>
           <t>Aug'25</t>
         </is>
       </c>
-      <c r="C7" s="94" t="inlineStr">
+      <c r="C7" s="96" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="94" t="n">
+      <c r="A8" s="96" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="94" t="inlineStr">
+      <c r="B8" s="96" t="inlineStr">
         <is>
           <t>Sep'25</t>
         </is>
       </c>
-      <c r="C8" s="94" t="inlineStr">
+      <c r="C8" s="96" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="D8" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="94" t="n">
+      <c r="A9" s="96" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="94" t="inlineStr">
+      <c r="B9" s="96" t="inlineStr">
         <is>
           <t>Oct'25</t>
         </is>
       </c>
-      <c r="C9" s="94" t="inlineStr">
+      <c r="C9" s="96" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="D9" s="94" t="n">
+      <c r="D9" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="94" t="n">
+      <c r="A10" s="96" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="94" t="inlineStr">
+      <c r="B10" s="96" t="inlineStr">
         <is>
           <t>Nov'25</t>
         </is>
       </c>
-      <c r="C10" s="94" t="inlineStr">
+      <c r="C10" s="96" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="D10" s="94" t="n">
+      <c r="D10" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="94" t="n">
+      <c r="A11" s="96" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="94" t="inlineStr">
+      <c r="B11" s="96" t="inlineStr">
         <is>
           <t>Dec'25</t>
         </is>
       </c>
-      <c r="C11" s="94" t="inlineStr">
+      <c r="C11" s="96" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="D11" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="94" t="n">
+      <c r="A12" s="96" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="94" t="inlineStr">
+      <c r="B12" s="96" t="inlineStr">
         <is>
           <t>Jan'25</t>
         </is>
       </c>
-      <c r="C12" s="94" t="inlineStr">
+      <c r="C12" s="96" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="D12" s="94" t="n">
+      <c r="D12" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="94" t="n">
+      <c r="A13" s="96" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="94" t="inlineStr">
+      <c r="B13" s="96" t="inlineStr">
         <is>
           <t>Feb'25</t>
         </is>
       </c>
-      <c r="C13" s="94" t="inlineStr">
+      <c r="C13" s="96" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D13" s="94" t="n">
+      <c r="D13" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="n">
+      <c r="A14" s="96" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="94" t="inlineStr">
+      <c r="B14" s="96" t="inlineStr">
         <is>
           <t>Mar'25</t>
         </is>
       </c>
-      <c r="C14" s="94" t="inlineStr">
+      <c r="C14" s="96" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D14" s="94" t="n">
+      <c r="D14" s="96" t="n">
         <v>2025</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="94" t="n">
+      <c r="A15" s="96" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="94" t="inlineStr">
+      <c r="B15" s="96" t="inlineStr">
         <is>
           <t>Apr'26</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
+      <c r="C15" s="96" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D15" s="94" t="n">
+      <c r="D15" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="94" t="n">
+      <c r="A16" s="96" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="94" t="inlineStr">
+      <c r="B16" s="96" t="inlineStr">
         <is>
           <t>May'26</t>
         </is>
       </c>
-      <c r="C16" s="94" t="inlineStr">
+      <c r="C16" s="96" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="D16" s="94" t="n">
+      <c r="D16" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="94" t="n">
+      <c r="A17" s="96" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="94" t="inlineStr">
+      <c r="B17" s="96" t="inlineStr">
         <is>
           <t>Jun'26</t>
         </is>
       </c>
-      <c r="C17" s="94" t="inlineStr">
+      <c r="C17" s="96" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="D17" s="94" t="n">
+      <c r="D17" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="94" t="n">
+      <c r="A18" s="96" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="94" t="inlineStr">
+      <c r="B18" s="96" t="inlineStr">
         <is>
           <t>Jul'26</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C18" s="96" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="D18" s="94" t="n">
+      <c r="D18" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="94" t="n">
+      <c r="A19" s="96" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="94" t="inlineStr">
+      <c r="B19" s="96" t="inlineStr">
         <is>
           <t>Aug'26</t>
         </is>
       </c>
-      <c r="C19" s="94" t="inlineStr">
+      <c r="C19" s="96" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="D19" s="94" t="n">
+      <c r="D19" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="94" t="n">
+      <c r="A20" s="96" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="94" t="inlineStr">
+      <c r="B20" s="96" t="inlineStr">
         <is>
           <t>Sep'26</t>
         </is>
       </c>
-      <c r="C20" s="94" t="inlineStr">
+      <c r="C20" s="96" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="D20" s="94" t="n">
+      <c r="D20" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="n">
+      <c r="A21" s="96" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="94" t="inlineStr">
+      <c r="B21" s="96" t="inlineStr">
         <is>
           <t>Oct'26</t>
         </is>
       </c>
-      <c r="C21" s="94" t="inlineStr">
+      <c r="C21" s="96" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="D21" s="94" t="n">
+      <c r="D21" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="94" t="n">
+      <c r="A22" s="96" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="94" t="inlineStr">
+      <c r="B22" s="96" t="inlineStr">
         <is>
           <t>Nov'26</t>
         </is>
       </c>
-      <c r="C22" s="94" t="inlineStr">
+      <c r="C22" s="96" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="D22" s="94" t="n">
+      <c r="D22" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="94" t="n">
+      <c r="A23" s="96" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="94" t="inlineStr">
+      <c r="B23" s="96" t="inlineStr">
         <is>
           <t>Dec'26</t>
         </is>
       </c>
-      <c r="C23" s="94" t="inlineStr">
+      <c r="C23" s="96" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="D23" s="94" t="n">
+      <c r="D23" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="94" t="n">
+      <c r="A24" s="96" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="94" t="inlineStr">
+      <c r="B24" s="96" t="inlineStr">
         <is>
           <t>Jan'26</t>
         </is>
       </c>
-      <c r="C24" s="94" t="inlineStr">
+      <c r="C24" s="96" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="D24" s="94" t="n">
+      <c r="D24" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="n">
+      <c r="A25" s="96" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="94" t="inlineStr">
+      <c r="B25" s="96" t="inlineStr">
         <is>
           <t>Feb'26</t>
         </is>
       </c>
-      <c r="C25" s="94" t="inlineStr">
+      <c r="C25" s="96" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D25" s="94" t="n">
+      <c r="D25" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="94" t="n">
+      <c r="A26" s="96" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="94" t="inlineStr">
+      <c r="B26" s="96" t="inlineStr">
         <is>
           <t>Mar'26</t>
         </is>
       </c>
-      <c r="C26" s="94" t="inlineStr">
+      <c r="C26" s="96" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D26" s="94" t="n">
+      <c r="D26" s="96" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="94" t="n">
+      <c r="A27" s="96" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="94" t="inlineStr">
+      <c r="B27" s="96" t="inlineStr">
         <is>
           <t>Apr'27</t>
         </is>
       </c>
-      <c r="C27" s="94" t="inlineStr">
+      <c r="C27" s="96" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="D27" s="94" t="n">
+      <c r="D27" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="94" t="n">
+      <c r="A28" s="96" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="94" t="inlineStr">
+      <c r="B28" s="96" t="inlineStr">
         <is>
           <t>May'27</t>
         </is>
       </c>
-      <c r="C28" s="94" t="inlineStr">
+      <c r="C28" s="96" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="D28" s="94" t="n">
+      <c r="D28" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="94" t="n">
+      <c r="A29" s="96" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="94" t="inlineStr">
+      <c r="B29" s="96" t="inlineStr">
         <is>
           <t>Jun'27</t>
         </is>
       </c>
-      <c r="C29" s="94" t="inlineStr">
+      <c r="C29" s="96" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="D29" s="94" t="n">
+      <c r="D29" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="94" t="n">
+      <c r="A30" s="96" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="94" t="inlineStr">
+      <c r="B30" s="96" t="inlineStr">
         <is>
           <t>Jul'27</t>
         </is>
       </c>
-      <c r="C30" s="94" t="inlineStr">
+      <c r="C30" s="96" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="D30" s="94" t="n">
+      <c r="D30" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="94" t="n">
+      <c r="A31" s="96" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="94" t="inlineStr">
+      <c r="B31" s="96" t="inlineStr">
         <is>
           <t>Aug'27</t>
         </is>
       </c>
-      <c r="C31" s="94" t="inlineStr">
+      <c r="C31" s="96" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="D31" s="94" t="n">
+      <c r="D31" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="94" t="n">
+      <c r="A32" s="96" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="94" t="inlineStr">
+      <c r="B32" s="96" t="inlineStr">
         <is>
           <t>Sep'27</t>
         </is>
       </c>
-      <c r="C32" s="94" t="inlineStr">
+      <c r="C32" s="96" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="D32" s="94" t="n">
+      <c r="D32" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="94" t="n">
+      <c r="A33" s="96" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="94" t="inlineStr">
+      <c r="B33" s="96" t="inlineStr">
         <is>
           <t>Oct'27</t>
         </is>
       </c>
-      <c r="C33" s="94" t="inlineStr">
+      <c r="C33" s="96" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="D33" s="94" t="n">
+      <c r="D33" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="94" t="n">
+      <c r="A34" s="96" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="94" t="inlineStr">
+      <c r="B34" s="96" t="inlineStr">
         <is>
           <t>Nov'27</t>
         </is>
       </c>
-      <c r="C34" s="94" t="inlineStr">
+      <c r="C34" s="96" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="D34" s="94" t="n">
+      <c r="D34" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="94" t="n">
+      <c r="A35" s="96" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="94" t="inlineStr">
+      <c r="B35" s="96" t="inlineStr">
         <is>
           <t>Dec'27</t>
         </is>
       </c>
-      <c r="C35" s="94" t="inlineStr">
+      <c r="C35" s="96" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="D35" s="94" t="n">
+      <c r="D35" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="94" t="n">
+      <c r="A36" s="96" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="94" t="inlineStr">
+      <c r="B36" s="96" t="inlineStr">
         <is>
           <t>Jan'27</t>
         </is>
       </c>
-      <c r="C36" s="94" t="inlineStr">
+      <c r="C36" s="96" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="D36" s="94" t="n">
+      <c r="D36" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="94" t="n">
+      <c r="A37" s="96" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="94" t="inlineStr">
+      <c r="B37" s="96" t="inlineStr">
         <is>
           <t>Feb'27</t>
         </is>
       </c>
-      <c r="C37" s="94" t="inlineStr">
+      <c r="C37" s="96" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="D37" s="94" t="n">
+      <c r="D37" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="94" t="n">
+      <c r="A38" s="96" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="94" t="inlineStr">
+      <c r="B38" s="96" t="inlineStr">
         <is>
           <t>Mar'27</t>
         </is>
       </c>
-      <c r="C38" s="94" t="inlineStr">
+      <c r="C38" s="96" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="D38" s="94" t="n">
+      <c r="D38" s="96" t="n">
         <v>2027</v>
       </c>
     </row>
@@ -19113,518 +19278,518 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="115" t="inlineStr">
+      <c r="A2" s="117" t="inlineStr">
         <is>
           <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="116" t="inlineStr">
+      <c r="A3" s="118" t="inlineStr">
         <is>
           <t>Rolling 3-month (M, M+1, M+2) demand forecast &amp; S&amp;OP planning model for Honasa / Mamaearth</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="116" t="inlineStr">
+      <c r="A4" s="118" t="inlineStr">
         <is>
           <t>Modern Trade. Combines statistical forecasting, business overlay and an AI-style ensemble,</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="116" t="inlineStr">
+      <c r="A5" s="118" t="inlineStr">
         <is>
           <t>then reconciles top-down target with bottom-up forecast across the full hierarchy.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="115" t="inlineStr">
+      <c r="A7" s="117" t="inlineStr">
         <is>
           <t>DATA (all real, no dummy numbers)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="116" t="inlineStr">
+      <c r="A8" s="118" t="inlineStr">
         <is>
           <t>Primary Sales History: real MT primary invoicing Apr'25–May'26, aggregated to Brand×Category</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="116" t="inlineStr">
+      <c r="A9" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   from PowerBI/RawDataFolders/Primary_Article_Monthly/*.csv.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="116" t="inlineStr">
+      <c r="A10" s="118" t="inlineStr">
         <is>
           <t>Offtake History: real store offtake (Apr'26–May'26) from Offtake_Monthly/*.csv.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="116" t="inlineStr">
+      <c r="A11" s="118" t="inlineStr">
         <is>
           <t>Monthly Target Upload: FY26-27 company NSV plan (seed).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="116" t="inlineStr">
+      <c r="A12" s="118" t="inlineStr">
         <is>
           <t>Distributor Master: real top ship-to accounts; service metrics are planner/DMS inputs (blue).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="116" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Contribution %, warehouse mapping etc. derive from the real primary footprint.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="115" t="inlineStr">
+      <c r="A15" s="117" t="inlineStr">
         <is>
           <t>ROLLING HORIZON</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="116" t="inlineStr">
+      <c r="A16" s="118" t="inlineStr">
         <is>
           <t>Control Panel → Last Actual Month and Forecast Month (M) drive everything.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="116" t="inlineStr">
+      <c r="A17" s="118" t="inlineStr">
         <is>
           <t>M+1, M+2 and all indices are derived via MATCH on the Calendar; advance Forecast Month by</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="116" t="inlineStr">
+      <c r="A18" s="118" t="inlineStr">
         <is>
           <t>one each cycle and the entire workbook rolls forward. Add a new month column to Primary Sales</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="116" t="inlineStr">
+      <c r="A19" s="118" t="inlineStr">
         <is>
           <t>History and update Last Actual Month to bring in a fresh actual.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="115" t="inlineStr">
+      <c r="A21" s="117" t="inlineStr">
         <is>
           <t>STATISTICAL METHODS (per Brand×Category, ₹ Cr)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="116" t="inlineStr">
+      <c r="A22" s="118" t="inlineStr">
         <is>
           <t>WMA            = w1·M-1 + w2·M-2 + w3·M-3, reseasonalised.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="116" t="inlineStr">
+      <c r="A23" s="118" t="inlineStr">
         <is>
           <t>Exp. Smoothing = normalised α(1-α)^k weighting of the last 6 months.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="116" t="inlineStr">
+      <c r="A24" s="118" t="inlineStr">
         <is>
           <t>Linear Trend   = last + (last − M-6)/5 · t, reseasonalised.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="116" t="inlineStr">
+      <c r="A25" s="118" t="inlineStr">
         <is>
           <t>Seasonal Index = 12-month mean × seasonal multiplier.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="116" t="inlineStr">
+      <c r="A26" s="118" t="inlineStr">
         <is>
           <t>CAGR           = last × (1+monthly CAGR)^t.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="116" t="inlineStr">
+      <c r="A27" s="118" t="inlineStr">
         <is>
           <t>Rolling Avg    = 3-month average, reseasonalised.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="116" t="inlineStr">
+      <c r="A28" s="118" t="inlineStr">
         <is>
           <t>YoY Growth     = same-month-last-year × (1 + YoY growth).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="116" t="inlineStr">
+      <c r="A29" s="118" t="inlineStr">
         <is>
           <t>Seasonal multiplier = category factor for the target month ÷ its 12-month average</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="116" t="inlineStr">
+      <c r="A30" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   (Seasonality Matrix; falls back to 100% if the category is absent).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="116" t="inlineStr">
+      <c r="A31" s="118" t="inlineStr">
         <is>
           <t>Statistical    = weight-normalised blend of the seven methods (weights on Control Panel).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="115" t="inlineStr">
+      <c r="A33" s="117" t="inlineStr">
         <is>
           <t>BUSINESS &amp; AI LAYERS</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="116" t="inlineStr">
+      <c r="A34" s="118" t="inlineStr">
         <is>
           <t>Business = Statistical × (1 + business adjustment % + promo uplift %). Promo uplift comes</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="116" t="inlineStr">
+      <c r="A35" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   from the Promotion Calendar (Brand×Category×Month).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="116" t="inlineStr">
+      <c r="A36" s="118" t="inlineStr">
         <is>
           <t>AI Ensemble = weighted blend of Statistical, Business and a driver-adjusted Statistical</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="116" t="inlineStr">
+      <c r="A37" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   (brand momentum + promo response), normalised by the three AI weights.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="116" t="inlineStr">
+      <c r="A38" s="118" t="inlineStr">
         <is>
           <t>Final (scenario) = AI × scenario multiplier + NPI loading (₹ Cr) for the month.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="115" t="inlineStr">
+      <c r="A40" s="117" t="inlineStr">
         <is>
           <t>SCENARIOS</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="116" t="inlineStr">
+      <c r="A41" s="118" t="inlineStr">
         <is>
           <t>Base / Optimistic / Conservative multipliers on the Control Panel scale the AI forecast.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="116" t="inlineStr">
+      <c r="A42" s="118" t="inlineStr">
         <is>
           <t>The Business Scenario selector drives the 'Selected' columns and the dashboard.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="115" t="inlineStr">
+      <c r="A44" s="117" t="inlineStr">
         <is>
           <t>TARGET DISTRIBUTION &amp; RECONCILIATION</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="116" t="inlineStr">
+      <c r="A45" s="118" t="inlineStr">
         <is>
           <t>Company 3-month target distributes to Zone / Chain / State / Article by real contribution %.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="116" t="inlineStr">
+      <c r="A46" s="118" t="inlineStr">
         <is>
           <t>Any level accepts an override (blue); the reconciliation line shows variance vs the company</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="116" t="inlineStr">
+      <c r="A47" s="118" t="inlineStr">
         <is>
           <t>control total so top-down and bottom-up always tie out.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="115" t="inlineStr">
+      <c r="A49" s="117" t="inlineStr">
         <is>
           <t>PRIMARY PLANNING</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="116" t="inlineStr">
+      <c r="A50" s="118" t="inlineStr">
         <is>
           <t>Suggested Primary = Expected Offtake (Base M) + Safety + Pipeline + Promo/NPI − Excess − Slow-moving.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="115" t="inlineStr">
+      <c r="A52" s="117" t="inlineStr">
         <is>
           <t>WAREHOUSES</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="116" t="inlineStr">
+      <c r="A53" s="118" t="inlineStr">
         <is>
           <t>Base forecast is split to Gurgaon / Mumbai / Bangalore / Kolkata by editable demand share,</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="116" t="inlineStr">
+      <c r="A54" s="118" t="inlineStr">
         <is>
           <t>checked against Control-Panel capacity; peak utilisation &gt;100% raises a reallocation alert.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="115" t="inlineStr">
+      <c r="A56" s="117" t="inlineStr">
         <is>
           <t>ACCURACY</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="116" t="inlineStr">
+      <c r="A57" s="118" t="inlineStr">
         <is>
           <t>1-month-ahead WMA back-test on real company primary: MAPE, WMAPE, Bias, Tracking Signal,</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="116" t="inlineStr">
+      <c r="A58" s="118" t="inlineStr">
         <is>
           <t>Accuracy % and MAE. Recomputes as new actual months are added.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="115" t="inlineStr">
+      <c r="A60" s="117" t="inlineStr">
         <is>
           <t>REFRESH STEPS (monthly)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="116" t="inlineStr">
+      <c r="A61" s="118" t="inlineStr">
         <is>
           <t>1. Paste the new month's primary into Primary Sales History (new column) and offtake into Offtake History.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="116" t="inlineStr">
+      <c r="A62" s="118" t="inlineStr">
         <is>
           <t>2. Set Control Panel → Last Actual Month = the new month; Forecast Month (M) = the next month.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="116" t="inlineStr">
+      <c r="A63" s="118" t="inlineStr">
         <is>
           <t>3. Update Promotion Calendar / NPI &amp; EPD for the new horizon; review Business Adj % in the engine.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="116" t="inlineStr">
+      <c r="A64" s="118" t="inlineStr">
         <is>
           <t>4. Review Scenario Summary, Warehouse Optimization and AI Business Insights for the S&amp;OP meeting.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="116" t="inlineStr">
+      <c r="A65" s="118" t="inlineStr">
         <is>
           <t>5. Capture manual changes in the Demand Planner Workbench (with reason) — the audit trail is preserved.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="116" t="inlineStr">
+      <c r="A66" s="118" t="inlineStr">
         <is>
           <t>Regenerate from source any time with:  python scripts/build_demand_forecast.py</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="115" t="inlineStr">
+      <c r="A68" s="117" t="inlineStr">
         <is>
           <t>BUSINESS EVENT ENGINE (separate module)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="116" t="inlineStr">
+      <c r="A69" s="118" t="inlineStr">
         <is>
           <t>Business_Event_Master: one row per activity (NPI, promo, distribution, institutional, …).</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="116" t="inlineStr">
+      <c r="A70" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   Only rows with Status = Approved affect the forecast; Baseline is never overwritten.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="116" t="inlineStr">
+      <c r="A71" s="118" t="inlineStr">
         <is>
           <t>Impact methods (any combination per event):</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="116" t="inlineStr">
+      <c r="A72" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   · Percentage uplift  — Base(brand×cat) × effective uplift %.</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="116" t="inlineStr">
+      <c r="A73" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   · Fixed additional qty — one-time, applied in the start month only.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="116" t="inlineStr">
+      <c r="A74" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   · Distribution gain  — New Stores × Units/Store, ramped up over the launch curve.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="116" t="inlineStr">
+      <c r="A75" s="118" t="inlineStr">
         <is>
           <t>Effective uplift = base uplift × Confidence × Priority weight × Category seasonality × ramp/decay.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="116" t="inlineStr">
+      <c r="A76" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   base uplift = explicit Expected Uplift %, else Chain Event Library, else Article Event Library.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="116" t="inlineStr">
+      <c r="A77" s="118" t="inlineStr">
         <is>
           <t>Ramp-up (NPI/structural) and decay (promo) curves are editable on Event Settings.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="116" t="inlineStr">
+      <c r="A78" s="118" t="inlineStr">
         <is>
           <t>Event Impact Engine combines OVERLAPPING % events MULTIPLICATIVELY — 1−Π(1+uᵢ), via EXP(Σln) —</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="116" t="inlineStr">
+      <c r="A79" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   so five promos on one Chain×Brand×Month do not naively add to +67%; absolute events are summed.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="116" t="inlineStr">
+      <c r="A80" s="118" t="inlineStr">
         <is>
           <t>Baseline, Event Uplift and Final are always shown side by side (Event Impact Engine / Dashboard).</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="116" t="inlineStr">
+      <c r="A81" s="118" t="inlineStr">
         <is>
           <t>Event Simulator: instant what-ifs (not gated by approval). Event Calendar: live timeline + impact.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="116" t="inlineStr">
+      <c r="A82" s="118" t="inlineStr">
         <is>
           <t>Demand Driver Library: reusable objects with historical learning → Recommended Uplift the planner</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="116" t="inlineStr">
+      <c r="A83" s="118" t="inlineStr">
         <is>
           <t xml:space="preserve">   can accept / modify / reject (AI-assisted planning, à la SAP IBP / Kinaxis / Blue Yonder).</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="116" t="inlineStr">
+      <c r="A84" s="118" t="inlineStr">
         <is>
           <t>Event horizon reference: Current month (M) + M+1 + M+2 tie to the baseline; ramp/decay project further.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="115" t="inlineStr">
+      <c r="A86" s="117" t="inlineStr">
         <is>
           <t>COLOUR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="116" t="inlineStr">
+      <c r="A87" s="118" t="inlineStr">
         <is>
           <t>Blue text on pale-yellow fill = editable input.   Black = formula.   Green = cross-sheet link.</t>
         </is>
@@ -23645,7 +23810,7 @@
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="C4:C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NPI Launch,Product Relaunch,New Listing,Distribution Expansion,Store Expansion,Visibility Campaign,Endcap,Power Wing,Gondola,SIS,Counter Display,Festival Promotion,BOGO,Price Drop,Retail Festival,Digital Campaign,TV Campaign,Influencer Campaign,Consumer Offer,Sampling Activity,Bundle Promotion,Combo Pack,Seasonal Push,New Warehouse Opening,New Distributor,Market Expansion,Export Order,Institutional Sales,Clearance Campaign"</formula1>
+      <formula1>'Event Settings'!$G$3:$G$31</formula1>
     </dataValidation>
     <dataValidation sqref="O4:O24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Percentage,Fixed Qty,Distribution Gain,Combined"</formula1>
